--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129173361</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -722,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492691</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005880</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,26 +784,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98560</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -873,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -918,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -950,58 +923,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129172413</v>
+        <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>100844</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492702</v>
+        <v>492541</v>
       </c>
       <c r="R4" t="n">
-        <v>7005781</v>
+        <v>7005833</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1030,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1040,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,6 +1018,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1072,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171609</v>
+        <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,13 +1090,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492541</v>
+        <v>492601</v>
       </c>
       <c r="R5" t="n">
-        <v>7005833</v>
+        <v>7005770</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1152,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171977</v>
+        <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,37 +1198,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492601</v>
+        <v>492523</v>
       </c>
       <c r="R6" t="n">
-        <v>7005770</v>
+        <v>7005882</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1277,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1313,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1339,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1453,58 +1451,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171507</v>
+        <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>97536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492523</v>
+        <v>492585</v>
       </c>
       <c r="R8" t="n">
-        <v>7005882</v>
+        <v>7005755</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1533,7 +1521,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1543,12 +1531,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1563,26 +1546,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1600,32 +1563,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129171793</v>
+        <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>97533</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1635,13 +1598,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492585</v>
+        <v>492602</v>
       </c>
       <c r="R9" t="n">
-        <v>7005755</v>
+        <v>7005837</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1668,21 +1631,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1691,11 +1644,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1712,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129173557</v>
+        <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,37 +1671,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492602</v>
+        <v>492590</v>
       </c>
       <c r="R10" t="n">
-        <v>7005837</v>
+        <v>7005936</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1780,11 +1736,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1793,6 +1764,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1809,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129171353</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,45 +1816,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492590</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005936</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1887,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1897,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1931,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2101,10 +2084,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129173052</v>
+        <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,13 +2119,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492710</v>
+        <v>492595</v>
       </c>
       <c r="R13" t="n">
-        <v>7005821</v>
+        <v>7005894</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2171,7 +2154,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2181,7 +2164,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2233,10 +2216,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129170873</v>
+        <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2244,47 +2227,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492543</v>
+        <v>492595</v>
       </c>
       <c r="R14" t="n">
-        <v>7005881</v>
+        <v>7005756</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2313,7 +2286,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2323,12 +2296,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,12 +2325,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2380,10 +2348,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129170649</v>
+        <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2415,13 +2383,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492595</v>
+        <v>492558</v>
       </c>
       <c r="R15" t="n">
         <v>7005894</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2450,7 +2418,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2460,7 +2428,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2512,37 +2485,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129172338</v>
+        <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>98563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2552,7 +2525,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2566,13 +2539,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492691</v>
+        <v>492616</v>
       </c>
       <c r="R16" t="n">
-        <v>7005745</v>
+        <v>7005716</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2601,7 +2574,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2611,12 +2584,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>1 fröställning i gammal granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2648,48 +2621,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129171830</v>
+        <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>100847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492595</v>
+        <v>492723</v>
       </c>
       <c r="R17" t="n">
-        <v>7005756</v>
+        <v>7005869</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2718,7 +2696,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2728,7 +2706,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2743,26 +2721,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2780,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171009</v>
+        <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2791,34 +2749,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492558</v>
+        <v>492643</v>
       </c>
       <c r="R18" t="n">
-        <v>7005894</v>
+        <v>7005955</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2850,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2860,12 +2823,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2894,12 +2852,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2917,52 +2875,47 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129172075</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>98560</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2971,10 +2924,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492616</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005716</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -3006,7 +2959,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3016,12 +2969,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 fröställning i gammal granskog.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3036,6 +2984,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3053,38 +3021,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129173109</v>
+        <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>100844</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3093,13 +3066,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492723</v>
+        <v>492518</v>
       </c>
       <c r="R20" t="n">
-        <v>7005869</v>
+        <v>7005861</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3128,7 +3101,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3138,7 +3111,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3153,6 +3131,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3170,10 +3168,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129173470</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3181,48 +3179,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492663</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005895</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3254,7 +3238,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3264,7 +3248,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3293,12 +3277,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3316,7 +3300,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129171549</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
         <v>57723</v>
@@ -3347,12 +3331,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3361,13 +3340,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492518</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005861</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3396,7 +3375,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3406,12 +3385,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3463,38 +3442,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129170389</v>
+        <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>91541</v>
+        <v>100847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3503,13 +3482,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492643</v>
+        <v>492624</v>
       </c>
       <c r="R23" t="n">
-        <v>7005955</v>
+        <v>7005951</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3538,7 +3517,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3548,7 +3527,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3563,26 +3542,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3600,62 +3559,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129170618</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492636</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005925</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3682,26 +3627,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3710,28 +3640,23 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129172151</v>
+        <v>129197762</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3760,24 +3685,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492661</v>
+        <v>492552</v>
       </c>
       <c r="R25" t="n">
-        <v>7005714</v>
+        <v>7005798</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3804,24 +3724,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3832,51 +3742,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129170332</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3904,17 +3789,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492645</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005964</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3941,21 +3826,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3964,79 +3839,61 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129171311</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>100844</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4045,13 +3902,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492624</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005951</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4080,7 +3937,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4090,7 +3947,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4105,6 +3967,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4119,6 +4001,4487 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129197748</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92226</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>492576</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7005792</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129197899</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>492662</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7005963</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129197745</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>492681</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7005731</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129197773</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>492702</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7005777</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129197771</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>492474</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7005814</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129197754</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>492459</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7005818</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129197778</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>492576</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7005799</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129197768</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78048</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492673</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7005936</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129197747</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92226</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>492738</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7005827</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129197777</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>492658</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7005841</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129197902</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>492671</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7005882</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt, över 100st bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129170873</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>492543</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7005881</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129197750</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492495</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7005861</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129197903</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492663</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7005892</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129197767</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>658</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492742</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7005805</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129197749</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>492626</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7005698</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129197774</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>492640</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7005697</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129197756</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>492452</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7005822</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129172338</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>492691</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7005745</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129197763</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>492563</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7005801</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129197752</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>492478</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7005840</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129197772</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>492699</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7005773</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129197901</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>658</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>492728</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7005767</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129197743</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>492617</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7005729</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129197740</v>
+      </c>
+      <c r="B52" t="n">
+        <v>83011</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>492677</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7005939</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129197776</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>492686</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7005861</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129197758</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>492465</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7005805</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129197741</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>492719</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7005791</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129197896</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92226</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>492539</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7005731</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129197755</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>492452</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7005823</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129197744</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>492718</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7005821</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129197770</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>492702</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7005794</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129197761</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>492512</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7005736</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129197759</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>492480</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7005779</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129197769</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>492718</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7005812</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129197757</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>492452</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7005819</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129197753</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>492487</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7005851</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129170618</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>492636</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7005925</v>
+      </c>
+      <c r="S65" t="n">
+        <v>9</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129197751</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>492493</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7005854</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129197742</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>492663</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7005860</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129197764</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>492665</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7005939</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129197760</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>492512</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7005743</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129197898</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>492653</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7005908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129197775</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Älggropbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>492591</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7005778</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2875,10 +2875,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129171549</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2886,36 +2886,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2924,10 +2920,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492518</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005861</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2959,7 +2955,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2969,7 +2965,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3021,10 +3022,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3032,32 +3033,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R20" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3101,7 +3106,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3111,12 +3116,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3559,32 +3559,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3630,6 +3630,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3656,32 +3661,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3727,11 +3732,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3855,60 +3855,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>92226</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3935,26 +3923,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3963,89 +3936,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92226</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4072,11 +4032,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4085,16 +4060,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4300,10 +4300,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91544</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4311,21 +4311,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R31" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4397,10 +4397,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91544</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,21 +4408,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R32" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4596,10 +4591,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4607,21 +4602,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5086,7 +5086,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129170873</v>
+        <v>129197750</v>
       </c>
       <c r="B39" t="n">
         <v>57723</v>
@@ -5115,29 +5115,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492543</v>
+        <v>492495</v>
       </c>
       <c r="R39" t="n">
-        <v>7005881</v>
+        <v>7005861</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5164,24 +5154,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5192,48 +5172,23 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B40" t="n">
         <v>57723</v>
@@ -5262,19 +5217,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R40" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5301,14 +5266,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,16 +5294,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197749</v>
+        <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492626</v>
+        <v>492640</v>
       </c>
       <c r="R43" t="n">
-        <v>7005698</v>
+        <v>7005697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5600,11 +5600,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5631,10 +5626,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197774</v>
+        <v>129197749</v>
       </c>
       <c r="B44" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5642,21 +5637,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492640</v>
+        <v>492626</v>
       </c>
       <c r="R44" t="n">
-        <v>7005697</v>
+        <v>7005698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5702,6 +5697,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5830,67 +5830,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129172338</v>
+        <v>129197763</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492691</v>
+        <v>492563</v>
       </c>
       <c r="R46" t="n">
-        <v>7005745</v>
+        <v>7005801</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5917,24 +5898,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5945,28 +5916,23 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -6001,10 +5967,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R47" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6068,10 +6034,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129197772</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6079,21 +6045,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6103,10 +6069,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492699</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005773</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6139,11 +6105,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6170,48 +6131,67 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197772</v>
+        <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492699</v>
+        <v>492691</v>
       </c>
       <c r="R49" t="n">
-        <v>7005773</v>
+        <v>7005745</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6238,11 +6218,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6251,26 +6246,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6962,21 +6962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7022,11 +7022,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7053,10 +7048,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,21 +7059,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7088,10 +7083,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7124,6 +7119,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7150,10 +7150,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B59" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7221,6 +7221,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7247,10 +7252,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>91540</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7258,21 +7263,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7318,11 +7323,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7451,10 +7451,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197769</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7462,21 +7462,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7486,10 +7486,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492718</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005812</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7522,6 +7522,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7650,10 +7655,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197753</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7661,21 +7666,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7685,10 +7690,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492487</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005851</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7721,11 +7726,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,62 +7752,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129170618</v>
+        <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492636</v>
+        <v>492663</v>
       </c>
       <c r="R65" t="n">
-        <v>7005925</v>
+        <v>7005860</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7834,26 +7820,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7862,21 +7833,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7985,48 +7951,62 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8053,11 +8033,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8066,26 +8061,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197764</v>
+        <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8093,21 +8093,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492665</v>
+        <v>492591</v>
       </c>
       <c r="R68" t="n">
-        <v>7005939</v>
+        <v>7005778</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,11 +8153,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8184,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
         <v>57723</v>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8259,7 +8254,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8286,7 +8281,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
         <v>57723</v>
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8361,7 +8356,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197775</v>
+        <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492591</v>
+        <v>492665</v>
       </c>
       <c r="R71" t="n">
-        <v>7005778</v>
+        <v>7005939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8459,6 +8454,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -2875,10 +2875,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2886,32 +2886,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2920,10 +2924,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2955,7 +2959,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2965,12 +2969,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3022,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129173470</v>
+        <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3033,36 +3032,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492663</v>
+        <v>492518</v>
       </c>
       <c r="R20" t="n">
-        <v>7005895</v>
+        <v>7005861</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3106,7 +3101,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,7 +3111,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197763</v>
+        <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5841,21 +5841,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492563</v>
+        <v>492699</v>
       </c>
       <c r="R46" t="n">
-        <v>7005801</v>
+        <v>7005773</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5901,11 +5901,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5932,48 +5927,67 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R47" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6000,14 +6014,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6018,26 +6042,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197772</v>
+        <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6045,21 +6074,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6069,10 +6098,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492699</v>
+        <v>492563</v>
       </c>
       <c r="R48" t="n">
-        <v>7005773</v>
+        <v>7005801</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6105,6 +6134,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6131,67 +6165,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129172338</v>
+        <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492691</v>
+        <v>492478</v>
       </c>
       <c r="R49" t="n">
-        <v>7005745</v>
+        <v>7005840</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6218,24 +6233,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,21 +6251,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98563</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1187,43 +1187,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171507</v>
+        <v>129173004</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1232,13 +1227,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492523</v>
+        <v>492703</v>
       </c>
       <c r="R6" t="n">
-        <v>7005882</v>
+        <v>7005807</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,12 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,26 +1287,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,38 +1304,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129171507</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492523</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005882</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1394,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,6 +1414,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3630,11 +3630,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3758,10 +3753,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3769,21 +3764,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3829,6 +3824,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4693,32 +4693,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78048</v>
+        <v>92226</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92226</v>
+        <v>78048</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197750</v>
+        <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5097,21 +5097,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492495</v>
+        <v>492663</v>
       </c>
       <c r="R39" t="n">
-        <v>7005861</v>
+        <v>7005892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5157,11 +5157,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5335,10 +5330,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B41" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5346,21 +5341,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5370,10 +5365,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5406,6 +5401,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5830,48 +5830,67 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197772</v>
+        <v>129172338</v>
       </c>
       <c r="B46" t="n">
-        <v>91544</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492699</v>
+        <v>492691</v>
       </c>
       <c r="R46" t="n">
-        <v>7005773</v>
+        <v>7005745</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5898,11 +5917,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5911,83 +5945,69 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129172338</v>
+        <v>129197772</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>91544</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492691</v>
+        <v>492699</v>
       </c>
       <c r="R47" t="n">
-        <v>7005745</v>
+        <v>7005773</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6014,26 +6034,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6042,28 +6047,23 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B48" t="n">
         <v>57723</v>
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R48" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6165,7 +6165,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197752</v>
+        <v>129197763</v>
       </c>
       <c r="B49" t="n">
         <v>57723</v>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492478</v>
+        <v>492563</v>
       </c>
       <c r="R49" t="n">
-        <v>7005840</v>
+        <v>7005801</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197740</v>
       </c>
       <c r="B51" t="n">
-        <v>91811</v>
+        <v>83011</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492677</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197743</v>
       </c>
       <c r="B52" t="n">
-        <v>83011</v>
+        <v>91526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492617</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6558,10 +6558,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B53" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R53" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6629,6 +6629,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,10 +6660,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6666,21 +6671,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6690,10 +6695,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R54" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6726,11 +6731,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6757,10 +6757,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>91491</v>
+        <v>92226</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6768,21 +6768,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R55" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>92226</v>
+        <v>91491</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R56" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7150,10 +7150,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>91540</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R59" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7221,11 +7221,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7252,10 +7247,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7263,21 +7258,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R60" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7323,6 +7318,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>91522</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7420,11 +7420,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7451,7 +7446,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
         <v>57723</v>
@@ -7486,10 +7481,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7553,7 +7548,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
         <v>57723</v>
@@ -7588,10 +7583,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,10 +7650,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7666,21 +7661,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7690,10 +7685,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7726,6 +7721,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,32 +7752,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197742</v>
+        <v>129197751</v>
       </c>
       <c r="B65" t="n">
-        <v>91491</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492663</v>
+        <v>492493</v>
       </c>
       <c r="R65" t="n">
-        <v>7005860</v>
+        <v>7005854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7823,6 +7823,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7849,32 +7854,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7884,10 +7889,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7920,11 +7925,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8082,10 +8082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197775</v>
+        <v>129197898</v>
       </c>
       <c r="B68" t="n">
-        <v>91544</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8093,21 +8093,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492591</v>
+        <v>492653</v>
       </c>
       <c r="R68" t="n">
-        <v>7005778</v>
+        <v>7005908</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,6 +8153,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8179,7 +8184,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B69" t="n">
         <v>57723</v>
@@ -8214,10 +8219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R69" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8254,7 +8259,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8281,7 +8286,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B70" t="n">
         <v>57723</v>
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8383,10 +8388,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197764</v>
+        <v>129197775</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>91544</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8394,21 +8399,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8418,10 +8423,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492665</v>
+        <v>492591</v>
       </c>
       <c r="R71" t="n">
-        <v>7005939</v>
+        <v>7005778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8454,11 +8459,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>98573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +926,7 @@
         <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,38 +1187,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129173004</v>
+        <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1227,13 +1232,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492703</v>
+        <v>492523</v>
       </c>
       <c r="R6" t="n">
-        <v>7005807</v>
+        <v>7005882</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1277,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,6 +1297,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,43 +1334,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171507</v>
+        <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>100857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1374,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492523</v>
+        <v>492703</v>
       </c>
       <c r="R7" t="n">
-        <v>7005882</v>
+        <v>7005807</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,12 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1434,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,37 +3179,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3238,7 +3243,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3248,7 +3253,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3277,12 +3287,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3300,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3311,42 +3321,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3375,7 +3380,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3385,12 +3390,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3570,21 +3570,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3630,6 +3630,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3656,32 +3661,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>91491</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3753,32 +3758,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>91497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3824,11 +3829,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3855,48 +3855,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>92226</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3923,11 +3935,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3936,76 +3963,89 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>92233</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,26 +4072,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4060,41 +4085,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4104,7 +4104,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4693,32 +4693,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B35" t="n">
-        <v>92226</v>
+        <v>78052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>78048</v>
+        <v>92233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4890,7 +4890,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129170873</v>
+        <v>129197750</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5212,29 +5212,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492543</v>
+        <v>492495</v>
       </c>
       <c r="R40" t="n">
-        <v>7005881</v>
+        <v>7005861</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5261,24 +5251,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5289,51 +5269,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5359,19 +5314,29 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R41" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5398,14 +5363,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5416,26 +5391,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197767</v>
+        <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492742</v>
+        <v>492626</v>
       </c>
       <c r="R42" t="n">
-        <v>7005805</v>
+        <v>7005698</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5503,6 +5503,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5529,10 +5534,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B43" t="n">
-        <v>91544</v>
+        <v>91818</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5540,21 +5545,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R43" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5626,10 +5631,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197749</v>
+        <v>129197774</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>91551</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5637,21 +5642,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5661,10 +5666,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492626</v>
+        <v>492640</v>
       </c>
       <c r="R44" t="n">
-        <v>7005698</v>
+        <v>7005697</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5697,11 +5702,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5731,7 +5731,7 @@
         <v>129197756</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,67 +5830,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129172338</v>
+        <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>91551</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492691</v>
+        <v>492699</v>
       </c>
       <c r="R46" t="n">
-        <v>7005745</v>
+        <v>7005773</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5917,26 +5898,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5945,31 +5911,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197772</v>
+        <v>129197752</v>
       </c>
       <c r="B47" t="n">
-        <v>91544</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5977,21 +5938,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6001,10 +5962,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492699</v>
+        <v>492478</v>
       </c>
       <c r="R47" t="n">
-        <v>7005773</v>
+        <v>7005840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6037,6 +5998,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6063,48 +6029,67 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6131,14 +6116,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6149,16 +6144,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6168,7 +6168,7 @@
         <v>129197763</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>83011</v>
+        <v>91818</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>83015</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6561,7 +6561,7 @@
         <v>129197758</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,10 +7446,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B63" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7653,7 +7653,7 @@
         <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>129197751</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7854,48 +7854,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B66" t="n">
-        <v>91491</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R66" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7922,11 +7936,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7935,78 +7964,69 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197742</v>
       </c>
       <c r="B67" t="n">
-        <v>98659</v>
+        <v>91497</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492663</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005860</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8033,26 +8053,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8061,31 +8066,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197898</v>
+        <v>129197764</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492653</v>
+        <v>492665</v>
       </c>
       <c r="R68" t="n">
-        <v>7005908</v>
+        <v>7005939</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8286,10 +8286,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197764</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492665</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005939</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8391,7 +8391,7 @@
         <v>129197775</v>
       </c>
       <c r="B71" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1055,48 +1055,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>100857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R5" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,26 +1155,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171507</v>
+        <v>129171977</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,47 +1183,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492523</v>
+        <v>492601</v>
       </c>
       <c r="R6" t="n">
-        <v>7005882</v>
+        <v>7005770</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,12 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,12 +1281,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,38 +1304,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129171507</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492523</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005882</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1394,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,6 +1414,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129170389</v>
+        <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,27 +2749,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492643</v>
+        <v>492518</v>
       </c>
       <c r="R18" t="n">
-        <v>7005955</v>
+        <v>7005861</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2813,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,7 +2828,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,7 +2885,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B19" t="n">
         <v>91551</v>
@@ -2903,16 +2913,7 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2924,10 +2925,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2959,7 +2960,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2969,7 +2970,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3021,10 +3022,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3032,32 +3033,36 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R20" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3101,7 +3106,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3111,12 +3116,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4693,32 +4693,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78052</v>
+        <v>92233</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92233</v>
+        <v>78052</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B50" t="n">
-        <v>91533</v>
+        <v>83015</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B51" t="n">
-        <v>91818</v>
+        <v>91533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B52" t="n">
-        <v>83015</v>
+        <v>91818</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6558,10 +6558,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6593,10 +6593,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R53" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6629,11 +6629,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6660,10 +6655,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6671,21 +6666,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6695,10 +6690,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R54" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6731,6 +6726,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8082,10 +8082,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197764</v>
+        <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8093,21 +8093,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492665</v>
+        <v>492591</v>
       </c>
       <c r="R68" t="n">
-        <v>7005939</v>
+        <v>7005778</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,11 +8153,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8184,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197898</v>
+        <v>129197764</v>
       </c>
       <c r="B69" t="n">
         <v>57725</v>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492653</v>
+        <v>492665</v>
       </c>
       <c r="R69" t="n">
-        <v>7005908</v>
+        <v>7005939</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8259,7 +8254,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8286,7 +8281,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B70" t="n">
         <v>57725</v>
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8361,7 +8356,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197775</v>
+        <v>129197760</v>
       </c>
       <c r="B71" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492591</v>
+        <v>492512</v>
       </c>
       <c r="R71" t="n">
-        <v>7005778</v>
+        <v>7005743</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8459,6 +8454,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>98580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98573</v>
+        <v>100864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1055,53 +1055,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129173004</v>
+        <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>100857</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492703</v>
+        <v>492601</v>
       </c>
       <c r="R5" t="n">
-        <v>7005807</v>
+        <v>7005770</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1150,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1172,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171977</v>
+        <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,37 +1198,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492601</v>
+        <v>492523</v>
       </c>
       <c r="R6" t="n">
-        <v>7005770</v>
+        <v>7005882</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1277,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,43 +1334,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171507</v>
+        <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>100864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1374,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492523</v>
+        <v>492703</v>
       </c>
       <c r="R7" t="n">
-        <v>7005882</v>
+        <v>7005807</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,12 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1434,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98573</v>
+        <v>98580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129170389</v>
       </c>
       <c r="B19" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>129173470</v>
       </c>
       <c r="B20" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,42 +3179,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3243,7 +3238,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3253,12 +3248,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3287,12 +3277,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3310,10 +3300,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3321,37 +3311,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3390,7 +3385,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3445,7 +3445,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3559,32 +3559,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3630,11 +3630,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3758,32 +3753,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3829,6 +3824,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3855,60 +3855,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>92240</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3935,26 +3923,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3963,89 +3936,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92233</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4072,11 +4032,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4085,16 +4060,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197749</v>
+        <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>91825</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492626</v>
+        <v>492742</v>
       </c>
       <c r="R42" t="n">
-        <v>7005698</v>
+        <v>7005805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5503,11 +5503,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5534,10 +5529,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91818</v>
+        <v>91558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5545,21 +5540,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5569,10 +5564,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R43" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5631,10 +5626,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197774</v>
+        <v>129197749</v>
       </c>
       <c r="B44" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5642,21 +5637,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5666,10 +5661,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492640</v>
+        <v>492626</v>
       </c>
       <c r="R44" t="n">
-        <v>7005697</v>
+        <v>7005698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5702,6 +5697,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5833,7 +5833,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197752</v>
+        <v>129197763</v>
       </c>
       <c r="B47" t="n">
         <v>57725</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492478</v>
+        <v>492563</v>
       </c>
       <c r="R47" t="n">
-        <v>7005840</v>
+        <v>7005801</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6029,67 +6029,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129172338</v>
+        <v>129197752</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492691</v>
+        <v>492478</v>
       </c>
       <c r="R48" t="n">
-        <v>7005745</v>
+        <v>7005840</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6116,24 +6097,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6144,69 +6115,83 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197763</v>
+        <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492563</v>
+        <v>492691</v>
       </c>
       <c r="R49" t="n">
-        <v>7005801</v>
+        <v>7005745</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6233,14 +6218,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6251,26 +6246,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>83015</v>
+        <v>91825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B51" t="n">
-        <v>91533</v>
+        <v>83005</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R51" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B52" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R52" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6561,7 +6561,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6962,21 +6962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7022,6 +7022,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7048,10 +7053,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7059,21 +7064,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7083,10 +7088,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7119,11 +7124,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7150,10 +7150,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B59" t="n">
-        <v>91547</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7221,6 +7221,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7247,10 +7252,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>91554</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7258,21 +7263,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7282,10 +7287,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7318,11 +7323,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7420,6 +7420,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7548,7 +7553,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197759</v>
+        <v>129197757</v>
       </c>
       <c r="B63" t="n">
         <v>57725</v>
@@ -7583,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492480</v>
+        <v>492452</v>
       </c>
       <c r="R63" t="n">
-        <v>7005779</v>
+        <v>7005819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7650,10 +7655,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197757</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>91536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7661,21 +7666,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7685,10 +7690,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005819</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7721,11 +7726,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,32 +7752,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>91504</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R65" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7823,11 +7823,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7854,62 +7849,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R66" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7936,24 +7917,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7964,69 +7935,78 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>91497</v>
+        <v>98676</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8053,11 +8033,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8066,16 +8061,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8085,7 +8085,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197764</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
         <v>57725</v>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492665</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005939</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8281,7 +8281,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
         <v>57725</v>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8383,7 +8383,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B71" t="n">
         <v>57725</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R71" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98580</v>
+        <v>98582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98580</v>
+        <v>98582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,32 +2749,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2783,10 +2787,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R18" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2818,7 +2822,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,12 +2832,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,7 +2887,7 @@
         <v>129170389</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3022,10 +3021,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129173470</v>
+        <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3033,36 +3032,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492663</v>
+        <v>492518</v>
       </c>
       <c r="R20" t="n">
-        <v>7005895</v>
+        <v>7005861</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3106,7 +3101,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3116,7 +3111,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3171,7 +3171,7 @@
         <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3559,32 +3559,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3727,6 +3727,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3753,32 +3758,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>91506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3788,10 +3793,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3824,11 +3829,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3858,7 +3858,7 @@
         <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4494,10 +4494,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4591,10 +4596,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4602,21 +4607,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4696,7 +4696,7 @@
         <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>78052</v>
+        <v>78054</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129197750</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>129197749</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         <v>129197756</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5830,48 +5830,67 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197772</v>
+        <v>129172338</v>
       </c>
       <c r="B46" t="n">
-        <v>91558</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492699</v>
+        <v>492691</v>
       </c>
       <c r="R46" t="n">
-        <v>7005773</v>
+        <v>7005745</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5898,11 +5917,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5911,26 +5945,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197763</v>
+        <v>129197772</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>91560</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5938,21 +5977,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5962,10 +6001,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492563</v>
+        <v>492699</v>
       </c>
       <c r="R47" t="n">
-        <v>7005801</v>
+        <v>7005773</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5998,11 +6037,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6029,10 +6063,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6064,10 +6098,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492563</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005801</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6131,67 +6165,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129172338</v>
+        <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492691</v>
+        <v>492478</v>
       </c>
       <c r="R49" t="n">
-        <v>7005745</v>
+        <v>7005840</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6218,24 +6233,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6246,31 +6251,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6364,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>83005</v>
+        <v>91827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6375,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6472,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6561,7 +6561,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,10 +7150,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>91556</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,21 +7161,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7185,10 +7185,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R59" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7221,11 +7221,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7252,10 +7247,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7263,21 +7258,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7287,10 +7282,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R60" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7323,6 +7318,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7349,10 +7349,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7420,11 +7420,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7451,10 +7446,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,10 +7481,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7553,10 +7548,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7588,10 +7583,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,10 +7650,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7666,21 +7661,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7690,10 +7685,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7726,6 +7721,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7755,7 +7755,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1055,48 +1055,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R5" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,26 +1155,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1334,53 +1319,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129171977</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492601</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005770</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,6 +1414,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B18" t="n">
         <v>91560</v>
@@ -2766,16 +2766,7 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2787,10 +2778,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R18" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2822,7 +2813,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2832,7 +2823,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2884,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
         <v>91560</v>
@@ -2912,7 +2903,16 @@
           <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,37 +3179,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3238,7 +3243,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3248,7 +3253,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3277,12 +3287,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3300,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3311,42 +3321,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3375,7 +3380,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3385,12 +3390,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3559,32 +3559,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>91506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3727,11 +3727,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3758,32 +3753,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>91506</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3793,10 +3788,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3829,6 +3824,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4494,10 +4494,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4596,10 +4591,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4607,21 +4602,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5830,67 +5830,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129172338</v>
+        <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492691</v>
+        <v>492699</v>
       </c>
       <c r="R46" t="n">
-        <v>7005745</v>
+        <v>7005773</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5917,26 +5898,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5945,31 +5911,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197772</v>
+        <v>129197763</v>
       </c>
       <c r="B47" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5977,21 +5938,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6001,10 +5962,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492699</v>
+        <v>492563</v>
       </c>
       <c r="R47" t="n">
-        <v>7005773</v>
+        <v>7005801</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6037,6 +5998,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6063,7 +6029,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -6098,10 +6064,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R48" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6165,48 +6131,67 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R49" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6233,14 +6218,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6251,16 +6246,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6951,10 +6951,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6962,21 +6962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7022,11 +7022,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7053,10 +7048,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7064,21 +7059,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7088,10 +7083,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7124,6 +7119,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8179,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R69" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8281,7 +8281,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197764</v>
+        <v>129197898</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492665</v>
+        <v>492653</v>
       </c>
       <c r="R71" t="n">
-        <v>7005939</v>
+        <v>7005908</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1055,53 +1055,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129173004</v>
+        <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>100866</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492703</v>
+        <v>492601</v>
       </c>
       <c r="R5" t="n">
-        <v>7005807</v>
+        <v>7005770</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,6 +1150,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1319,48 +1334,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R7" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1434,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3179,42 +3179,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3243,7 +3238,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3253,12 +3248,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3287,12 +3277,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3310,10 +3300,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3321,37 +3311,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3380,7 +3375,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3390,7 +3385,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3419,12 +3419,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98582</v>
+        <v>98608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98582</v>
+        <v>98608</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3168,48 +3168,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129171311</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>100892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492624</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005951</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3238,7 +3243,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3248,7 +3253,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3263,26 +3268,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3300,10 +3285,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3311,42 +3296,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3375,7 +3355,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3385,12 +3365,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3419,12 +3394,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3442,38 +3417,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129171311</v>
+        <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>100866</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3482,13 +3457,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492624</v>
+        <v>492661</v>
       </c>
       <c r="R23" t="n">
-        <v>7005951</v>
+        <v>7005714</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3517,7 +3492,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3527,7 +3502,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3542,6 +3522,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3562,7 +3562,7 @@
         <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3855,48 +3855,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3923,11 +3935,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3936,76 +3963,89 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>92257</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4032,26 +4072,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4060,41 +4085,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4206,7 +4206,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4693,32 +4693,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B35" t="n">
-        <v>92242</v>
+        <v>78054</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,32 +4790,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>78054</v>
+        <v>92257</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4890,7 +4890,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6757,10 +6757,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B55" t="n">
-        <v>92242</v>
+        <v>91504</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6768,21 +6768,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R55" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B56" t="n">
-        <v>91506</v>
+        <v>92257</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,10 +6889,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R56" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6954,7 +6954,7 @@
         <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7360,21 +7360,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7384,10 +7384,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7420,6 +7420,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7446,7 +7451,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7481,10 +7486,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7548,7 +7553,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197757</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -7583,10 +7588,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492452</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7650,10 +7655,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197757</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7661,21 +7666,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7685,10 +7690,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005819</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7721,11 +7726,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7755,7 +7755,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8281,7 +8281,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197764</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492665</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005939</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197898</v>
+        <v>129197764</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492653</v>
+        <v>492665</v>
       </c>
       <c r="R71" t="n">
-        <v>7005908</v>
+        <v>7005939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98608</v>
+        <v>98609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98608</v>
+        <v>98609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B18" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2758,15 +2758,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R18" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2813,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2823,7 +2828,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,10 +2880,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B19" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2895,24 +2900,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2924,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2959,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2969,7 +2961,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,53 +3160,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171311</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>100892</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492624</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005951</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3243,7 +3230,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3253,7 +3240,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3268,6 +3255,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3285,10 +3292,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3296,37 +3303,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3355,7 +3367,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3365,7 +3377,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3394,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3417,38 +3434,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129172151</v>
+        <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>100894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3457,13 +3474,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492661</v>
+        <v>492624</v>
       </c>
       <c r="R23" t="n">
-        <v>7005714</v>
+        <v>7005951</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3492,7 +3509,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3502,12 +3519,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3522,26 +3534,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3656,10 +3648,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3667,21 +3659,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3691,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3727,6 +3719,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3753,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3764,21 +3761,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3788,10 +3785,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3824,11 +3821,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3855,60 +3847,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>92258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3935,26 +3915,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3963,89 +3928,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92257</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4072,11 +4024,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4085,16 +4052,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4400,7 +4392,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4417,14 +4409,10 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4494,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4505,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4529,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4565,6 +4553,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4591,10 +4584,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4602,21 +4595,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4626,10 +4619,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4662,11 +4655,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4793,7 +4781,7 @@
         <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4890,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4907,14 +4895,10 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4987,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,7 +5073,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5106,14 +5090,10 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5435,7 +5415,7 @@
         <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5532,7 +5512,7 @@
         <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5549,14 +5529,10 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5833,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5850,14 +5826,10 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6134,7 +6106,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6267,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6278,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6302,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6364,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197740</v>
       </c>
       <c r="B51" t="n">
-        <v>91837</v>
+        <v>83007</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6375,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6399,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492677</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6461,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197743</v>
       </c>
       <c r="B52" t="n">
-        <v>83007</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6472,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492617</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6558,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B53" t="n">
-        <v>91558</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,21 +6541,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6593,10 +6565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R53" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6629,6 +6601,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,10 +6632,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6666,23 +6643,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6690,10 +6663,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R54" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6726,11 +6699,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6757,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>91504</v>
+        <v>92258</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6768,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6792,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R55" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6854,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>92257</v>
+        <v>91504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R56" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6951,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6962,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7022,6 +6990,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7048,10 +7021,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7059,21 +7032,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7083,10 +7056,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7119,11 +7092,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7150,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B59" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7161,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7185,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7221,6 +7189,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7247,10 +7220,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7258,21 +7231,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7282,10 +7255,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7318,11 +7291,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7451,7 +7419,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197757</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7486,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492452</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005819</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7553,10 +7521,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197769</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7564,21 +7532,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7588,10 +7556,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005812</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7624,11 +7592,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7655,10 +7618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197753</v>
       </c>
       <c r="B64" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7666,21 +7629,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7690,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492487</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005851</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7726,6 +7689,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,48 +7720,62 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B65" t="n">
-        <v>91504</v>
+        <v>98705</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R65" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7820,11 +7802,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7833,48 +7830,53 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7884,10 +7886,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7920,11 +7922,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7951,62 +7948,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8033,24 +8016,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,21 +8034,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8085,7 +8053,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8102,14 +8070,10 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98609</v>
+        <v>98610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98609</v>
+        <v>98610</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3636,22 +3636,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3721,11 +3721,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3738,22 +3733,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,21 +3756,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3823,6 +3818,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3835,12 +3835,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3932,12 +3932,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4183,12 +4183,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4280,12 +4280,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4377,12 +4377,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4470,22 +4470,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4555,11 +4555,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4572,22 +4567,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4595,21 +4590,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4657,6 +4652,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4669,44 +4669,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78054</v>
+        <v>92258</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4766,44 +4766,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92258</v>
+        <v>78054</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,12 +4863,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4956,12 +4956,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5058,12 +5058,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5151,12 +5151,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5253,12 +5253,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B42" t="n">
-        <v>91838</v>
+        <v>91560</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,23 +5423,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5447,10 +5443,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R42" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5497,22 +5493,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197774</v>
+        <v>129197749</v>
       </c>
       <c r="B43" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,19 +5516,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492640</v>
+        <v>492626</v>
       </c>
       <c r="R43" t="n">
-        <v>7005697</v>
+        <v>7005698</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5578,6 +5578,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5590,19 +5595,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197749</v>
+        <v>129197756</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5637,10 +5642,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492626</v>
+        <v>492452</v>
       </c>
       <c r="R44" t="n">
-        <v>7005698</v>
+        <v>7005822</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5692,22 +5697,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129197756</v>
+        <v>129197767</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5715,21 +5720,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492452</v>
+        <v>492742</v>
       </c>
       <c r="R45" t="n">
-        <v>7005822</v>
+        <v>7005805</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5777,11 +5782,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5794,12 +5794,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5887,12 +5887,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5989,12 +5989,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6091,12 +6091,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6324,22 +6324,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>83007</v>
+        <v>91838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6421,22 +6421,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>83007</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6518,22 +6518,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,23 +6541,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R53" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6603,11 +6599,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6620,22 +6611,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6643,19 +6634,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R54" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6701,6 +6696,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6713,12 +6713,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6810,12 +6810,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6907,22 +6907,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6992,11 +6992,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7009,22 +7004,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7032,21 +7027,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7056,10 +7051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7094,6 +7089,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7106,22 +7106,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91554</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R59" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7191,11 +7191,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7208,22 +7203,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,21 +7226,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7255,10 +7250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R60" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7293,6 +7288,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7305,22 +7305,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7390,11 +7390,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7407,19 +7402,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197757</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7454,10 +7449,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492452</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005819</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7509,22 +7504,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197769</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7532,21 +7527,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492718</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005812</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7594,6 +7589,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7606,19 +7606,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197753</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492487</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005851</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7708,74 +7708,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B65" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R65" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7802,24 +7788,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7830,21 +7806,16 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7936,60 +7907,74 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8016,14 +8001,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8034,16 +8029,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8131,12 +8131,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8233,12 +8233,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8335,12 +8335,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8437,12 +8437,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
         <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98610</v>
+        <v>98614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2762,16 +2762,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R18" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2818,7 +2809,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,7 +2819,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2880,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,7 +2895,16 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3163,7 +3163,7 @@
         <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91507</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3847,48 +3847,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>92258</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3915,11 +3927,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3928,76 +3955,89 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4024,26 +4064,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4052,41 +4077,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91560</v>
+        <v>91841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,19 +5423,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5443,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R42" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5505,10 +5509,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197749</v>
+        <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,23 +5520,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492626</v>
+        <v>492640</v>
       </c>
       <c r="R43" t="n">
-        <v>7005698</v>
+        <v>7005697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5576,11 +5576,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5607,7 +5602,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197756</v>
+        <v>129197749</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5642,10 +5637,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492452</v>
+        <v>492626</v>
       </c>
       <c r="R44" t="n">
-        <v>7005822</v>
+        <v>7005698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5709,10 +5704,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129197767</v>
+        <v>129197756</v>
       </c>
       <c r="B45" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5720,21 +5715,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492742</v>
+        <v>492452</v>
       </c>
       <c r="R45" t="n">
-        <v>7005805</v>
+        <v>7005822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5780,6 +5775,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5809,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>83011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197743</v>
       </c>
       <c r="B52" t="n">
-        <v>83007</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492617</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B59" t="n">
-        <v>91554</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7189,6 +7189,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7215,10 +7220,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>91557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7226,21 +7231,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7250,10 +7255,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7286,11 +7291,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7320,7 +7320,7 @@
         <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7720,32 +7720,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R65" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7791,11 +7791,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,48 +7817,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B66" t="n">
-        <v>91504</v>
+        <v>98710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R66" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7890,11 +7899,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7903,78 +7927,69 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8001,24 +8016,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8029,31 +8034,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197775</v>
+        <v>129197898</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8061,19 +8061,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8081,10 +8085,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492591</v>
+        <v>492653</v>
       </c>
       <c r="R68" t="n">
-        <v>7005778</v>
+        <v>7005908</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8117,6 +8121,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8143,7 +8152,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8178,10 +8187,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R69" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8218,7 +8227,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8245,7 +8254,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8280,10 +8289,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8347,10 +8356,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197764</v>
+        <v>129197775</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8358,23 +8367,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8382,10 +8387,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492665</v>
+        <v>492591</v>
       </c>
       <c r="R71" t="n">
-        <v>7005939</v>
+        <v>7005778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8418,11 +8423,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3171,37 +3171,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3240,7 +3245,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3269,12 +3279,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3292,10 +3302,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3303,42 +3313,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3367,7 +3372,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3377,12 +3382,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3847,60 +3847,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>92261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3927,26 +3915,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3955,89 +3928,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92261</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4064,11 +4024,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4077,16 +4052,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,6 +4553,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4579,10 +4584,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4590,21 +4595,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4614,10 +4619,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4650,11 +4655,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,19 +5081,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5101,10 +5105,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R39" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5137,6 +5141,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,7 +5172,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5192,19 +5201,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R40" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,14 +5250,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5249,26 +5278,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5276,47 +5330,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R41" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5343,26 +5383,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,41 +5396,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -7118,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91557</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R59" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7189,11 +7189,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7220,10 +7215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>91557</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,21 +7226,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7255,10 +7250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R60" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7291,6 +7286,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98614</v>
+        <v>100901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100899</v>
+        <v>98616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +926,7 @@
         <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
         <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98614</v>
+        <v>98616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>91509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>91507</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
         <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,11 +4553,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,10 +4579,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4595,21 +4590,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4655,6 +4650,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B35" t="n">
-        <v>92261</v>
+        <v>78057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>78056</v>
+        <v>92263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197750</v>
+        <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,23 +5081,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5105,10 +5101,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492495</v>
+        <v>492663</v>
       </c>
       <c r="R39" t="n">
-        <v>7005861</v>
+        <v>7005892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5141,11 +5137,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5172,7 +5163,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129170873</v>
+        <v>129197750</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5201,29 +5192,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492543</v>
+        <v>492495</v>
       </c>
       <c r="R40" t="n">
-        <v>7005881</v>
+        <v>7005861</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5250,24 +5231,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5278,51 +5249,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,33 +5276,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492543</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5383,11 +5343,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5396,16 +5371,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
         <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>83011</v>
+        <v>91843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B51" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>83012</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B55" t="n">
-        <v>92261</v>
+        <v>91509</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R55" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B56" t="n">
-        <v>91507</v>
+        <v>92263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R56" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>91543</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,6 +6990,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7016,10 +7021,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7027,21 +7032,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7051,10 +7056,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7087,11 +7092,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7121,7 +7121,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7817,62 +7817,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R66" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7899,24 +7885,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7927,69 +7903,78 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8016,14 +8001,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8034,16 +8029,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197764</v>
+        <v>129197775</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8265,23 +8265,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8289,10 +8285,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492665</v>
+        <v>492591</v>
       </c>
       <c r="R70" t="n">
-        <v>7005939</v>
+        <v>7005778</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8325,11 +8321,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8356,10 +8347,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197775</v>
+        <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>91563</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,19 +8358,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8387,10 +8382,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492591</v>
+        <v>492665</v>
       </c>
       <c r="R71" t="n">
-        <v>7005778</v>
+        <v>7005939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8423,6 +8418,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100901</v>
+        <v>98620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98616</v>
+        <v>100905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171977</v>
+        <v>129171507</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,37 +1066,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492601</v>
+        <v>492523</v>
       </c>
       <c r="R5" t="n">
-        <v>7005770</v>
+        <v>7005882</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1135,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1145,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,12 +1179,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171507</v>
+        <v>129171977</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,47 +1213,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492523</v>
+        <v>492601</v>
       </c>
       <c r="R6" t="n">
-        <v>7005882</v>
+        <v>7005770</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1272,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1277,12 +1282,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98616</v>
+        <v>98620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3171,42 +3171,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,12 +3240,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3279,12 +3269,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3302,10 +3292,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,37 +3303,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3382,7 +3377,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>91509</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3847,48 +3847,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>92263</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3915,11 +3927,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3928,76 +3955,89 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>92267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4024,26 +4064,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4052,41 +4077,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B39" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,19 +5081,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5101,10 +5105,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R39" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5137,6 +5141,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,7 +5172,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5192,19 +5201,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R40" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,14 +5250,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5249,26 +5278,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5276,47 +5330,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R41" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5343,26 +5383,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,51 +5396,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B42" t="n">
-        <v>91843</v>
+        <v>91569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,23 +5423,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5447,10 +5443,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R42" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5509,10 +5505,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B43" t="n">
-        <v>91565</v>
+        <v>91847</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,19 +5516,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R43" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5899,48 +5899,67 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197763</v>
+        <v>129172338</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492563</v>
+        <v>492691</v>
       </c>
       <c r="R47" t="n">
-        <v>7005801</v>
+        <v>7005745</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5967,14 +5986,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5985,23 +6014,28 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129197763</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -6036,10 +6070,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492563</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005801</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6103,67 +6137,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129172338</v>
+        <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492691</v>
+        <v>492478</v>
       </c>
       <c r="R49" t="n">
-        <v>7005745</v>
+        <v>7005840</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6190,24 +6205,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,31 +6223,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B53" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,19 +6541,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6561,10 +6565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R53" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,6 +6601,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6623,10 +6632,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6634,23 +6643,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R54" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6694,11 +6699,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>91509</v>
+        <v>92267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R55" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>92263</v>
+        <v>91513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R56" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,11 +6990,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7021,10 +7016,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7032,21 +7027,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7056,10 +7051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7092,6 +7087,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7121,7 +7121,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>91541</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,6 +7388,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7414,7 +7419,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7449,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7516,7 +7521,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197757</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492452</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7618,10 +7623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197757</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>91545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7629,21 +7634,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7653,10 +7658,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005819</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7689,11 +7694,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7723,7 +7723,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7817,48 +7817,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7885,14 +7899,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7903,78 +7927,69 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8001,24 +8016,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8029,31 +8034,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197898</v>
+        <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8061,23 +8061,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8085,10 +8081,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492653</v>
+        <v>492591</v>
       </c>
       <c r="R68" t="n">
-        <v>7005908</v>
+        <v>7005778</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8121,11 +8117,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8254,10 +8245,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197775</v>
+        <v>129197898</v>
       </c>
       <c r="B70" t="n">
-        <v>91565</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8265,19 +8256,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8285,10 +8280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492591</v>
+        <v>492653</v>
       </c>
       <c r="R70" t="n">
-        <v>7005778</v>
+        <v>7005908</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8321,6 +8316,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98620</v>
+        <v>98628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171507</v>
+        <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,47 +1066,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492523</v>
+        <v>492601</v>
       </c>
       <c r="R5" t="n">
-        <v>7005882</v>
+        <v>7005770</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1145,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,12 +1164,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,48 +1187,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>100913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R6" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1272,7 +1262,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1282,7 +1272,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,26 +1287,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,38 +1304,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129171507</v>
       </c>
       <c r="B7" t="n">
-        <v>100905</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492523</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005882</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1394,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,6 +1414,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98620</v>
+        <v>98628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3171,37 +3171,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3240,7 +3245,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3269,12 +3279,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3292,10 +3302,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3303,42 +3313,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3367,7 +3372,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3377,12 +3382,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>91513</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3847,60 +3847,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>92268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3927,26 +3915,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3955,89 +3928,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92267</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4064,11 +4024,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4077,16 +4052,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,23 +4303,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R31" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4389,10 +4385,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B32" t="n">
-        <v>91569</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4400,19 +4396,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R32" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78057</v>
+        <v>92268</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92267</v>
+        <v>78057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197750</v>
+        <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,23 +5081,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5105,10 +5101,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492495</v>
+        <v>492663</v>
       </c>
       <c r="R39" t="n">
-        <v>7005861</v>
+        <v>7005892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5141,11 +5137,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5172,7 +5163,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129170873</v>
+        <v>129197750</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5201,29 +5192,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492543</v>
+        <v>492495</v>
       </c>
       <c r="R40" t="n">
-        <v>7005881</v>
+        <v>7005861</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5250,24 +5231,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5278,51 +5249,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>91569</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,33 +5276,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492543</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5383,11 +5343,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5396,16 +5371,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
         <v>129197774</v>
       </c>
       <c r="B42" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>129197767</v>
       </c>
       <c r="B43" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5899,67 +5899,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129172338</v>
+        <v>129197763</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492691</v>
+        <v>492563</v>
       </c>
       <c r="R47" t="n">
-        <v>7005745</v>
+        <v>7005801</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5986,24 +5967,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6014,28 +5985,23 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -6070,10 +6036,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R48" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6137,48 +6103,67 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R49" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6205,14 +6190,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,26 +6218,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197740</v>
       </c>
       <c r="B51" t="n">
-        <v>91847</v>
+        <v>83012</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492677</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005939</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197743</v>
       </c>
       <c r="B52" t="n">
-        <v>83012</v>
+        <v>91550</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492617</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005729</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6635,7 +6635,7 @@
         <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B55" t="n">
-        <v>92267</v>
+        <v>91514</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R55" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B56" t="n">
-        <v>91513</v>
+        <v>92268</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R56" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,6 +6990,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7016,10 +7021,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7027,21 +7032,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7051,10 +7056,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7087,11 +7092,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7121,7 +7121,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,11 +7388,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7419,7 +7414,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7454,10 +7449,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7521,7 +7516,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,10 +7618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>91545</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7634,21 +7629,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7658,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7694,6 +7689,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7723,7 +7723,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7817,62 +7817,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R66" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7899,24 +7885,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7927,69 +7903,78 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8016,14 +8001,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8034,16 +8029,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171977</v>
+        <v>129171507</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,37 +1066,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492601</v>
+        <v>492523</v>
       </c>
       <c r="R5" t="n">
-        <v>7005770</v>
+        <v>7005882</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1135,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1145,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,12 +1179,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,53 +1202,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129173004</v>
+        <v>129171977</v>
       </c>
       <c r="B6" t="n">
-        <v>100913</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492703</v>
+        <v>492601</v>
       </c>
       <c r="R6" t="n">
-        <v>7005807</v>
+        <v>7005770</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,7 +1272,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1272,7 +1282,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,6 +1297,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1304,43 +1334,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171507</v>
+        <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1374,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492523</v>
+        <v>492703</v>
       </c>
       <c r="R7" t="n">
-        <v>7005882</v>
+        <v>7005807</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,12 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1434,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3160,38 +3160,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129172151</v>
+        <v>129171311</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492661</v>
+        <v>492624</v>
       </c>
       <c r="R21" t="n">
-        <v>7005714</v>
+        <v>7005951</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,12 +3245,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3265,26 +3260,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3434,38 +3409,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129171311</v>
+        <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>100913</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3474,13 +3449,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492624</v>
+        <v>492661</v>
       </c>
       <c r="R23" t="n">
-        <v>7005951</v>
+        <v>7005714</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3509,7 +3484,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3519,7 +3494,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3534,6 +3514,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3659,21 +3659,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3719,6 +3719,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3745,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3816,11 +3821,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>91564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,19 +4303,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R31" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4385,10 +4389,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91564</v>
+        <v>91570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4396,23 +4400,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R32" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,6 +4553,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4579,10 +4584,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4590,21 +4595,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4614,10 +4619,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4650,11 +4655,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B35" t="n">
-        <v>92268</v>
+        <v>78057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>78057</v>
+        <v>92268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5412,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91570</v>
+        <v>91848</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,19 +5423,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5443,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R42" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5505,10 +5509,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91848</v>
+        <v>91570</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,23 +5520,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R43" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>91848</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91550</v>
+        <v>83012</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,23 +6541,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R53" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6601,11 +6597,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6632,10 +6623,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6643,19 +6634,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R54" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6699,6 +6694,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>91514</v>
+        <v>92268</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R55" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>92268</v>
+        <v>91514</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R56" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,11 +6990,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7021,10 +7016,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7032,21 +7027,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7056,10 +7051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7092,6 +7087,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7720,32 +7720,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197742</v>
+        <v>129197751</v>
       </c>
       <c r="B65" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492663</v>
+        <v>492493</v>
       </c>
       <c r="R65" t="n">
-        <v>7005860</v>
+        <v>7005854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7791,6 +7791,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7817,48 +7822,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7885,14 +7904,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7903,78 +7932,69 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197742</v>
       </c>
       <c r="B67" t="n">
-        <v>98724</v>
+        <v>91514</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492663</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005860</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8001,26 +8021,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8029,21 +8034,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98628</v>
+        <v>100913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100913</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3160,53 +3160,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171311</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>100913</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492624</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005951</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,7 +3240,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3260,6 +3255,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3277,10 +3292,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3288,37 +3303,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3347,7 +3367,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3357,7 +3377,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3386,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3409,38 +3434,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129172151</v>
+        <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>100913</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3449,13 +3474,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492661</v>
+        <v>492624</v>
       </c>
       <c r="R23" t="n">
-        <v>7005714</v>
+        <v>7005951</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3484,7 +3509,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3494,12 +3519,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3514,26 +3534,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3719,11 +3719,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3750,10 +3745,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,21 +3756,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3821,6 +3816,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B31" t="n">
-        <v>91564</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,23 +4303,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R31" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4389,10 +4385,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B32" t="n">
-        <v>91570</v>
+        <v>91564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4400,19 +4396,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R32" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,11 +4553,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,10 +4579,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4595,21 +4590,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4655,6 +4650,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B39" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,19 +5081,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5101,10 +5105,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R39" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5137,6 +5141,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,7 +5172,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5192,19 +5201,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R40" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,14 +5250,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5249,26 +5278,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91570</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5276,47 +5330,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R41" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5343,26 +5383,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,41 +5396,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197740</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492677</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B51" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B52" t="n">
-        <v>83012</v>
+        <v>91848</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7720,32 +7720,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91514</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R65" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7791,11 +7791,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,62 +7817,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R66" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7904,24 +7885,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7932,69 +7903,78 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197742</v>
+        <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>91514</v>
+        <v>98724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492663</v>
+        <v>492636</v>
       </c>
       <c r="R67" t="n">
-        <v>7005860</v>
+        <v>7005925</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8021,11 +8001,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8034,16 +8029,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100913</v>
+        <v>98631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>100916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98628</v>
+        <v>98631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3160,48 +3160,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129171311</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>100916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492624</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005951</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3240,7 +3245,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3255,26 +3260,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3434,53 +3419,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129171311</v>
+        <v>129170332</v>
       </c>
       <c r="B23" t="n">
-        <v>100913</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492624</v>
+        <v>492645</v>
       </c>
       <c r="R23" t="n">
-        <v>7005951</v>
+        <v>7005964</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3509,7 +3489,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3519,7 +3499,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3534,6 +3514,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3648,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B25" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3719,6 +3719,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3745,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3816,11 +3821,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3850,7 +3850,7 @@
         <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>91567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,19 +4303,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R31" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4385,10 +4389,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91564</v>
+        <v>91573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4396,23 +4400,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R32" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78057</v>
+        <v>92271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92268</v>
+        <v>78057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197750</v>
+        <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,23 +5081,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5105,10 +5101,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492495</v>
+        <v>492663</v>
       </c>
       <c r="R39" t="n">
-        <v>7005861</v>
+        <v>7005892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5141,11 +5137,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5172,7 +5163,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129170873</v>
+        <v>129197750</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5201,29 +5192,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492543</v>
+        <v>492495</v>
       </c>
       <c r="R40" t="n">
-        <v>7005881</v>
+        <v>7005861</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5250,24 +5231,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5278,51 +5249,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,33 +5276,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492543</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5383,11 +5343,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5396,26 +5371,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197767</v>
+        <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,21 +5423,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5447,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492742</v>
+        <v>492626</v>
       </c>
       <c r="R42" t="n">
-        <v>7005805</v>
+        <v>7005698</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5483,6 +5483,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5509,10 +5514,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B43" t="n">
-        <v>91570</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,19 +5525,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5549,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R43" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5602,10 +5611,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197749</v>
+        <v>129197774</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5613,23 +5622,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5637,10 +5642,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492626</v>
+        <v>492640</v>
       </c>
       <c r="R44" t="n">
-        <v>7005698</v>
+        <v>7005697</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5673,11 +5678,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5809,7 +5809,7 @@
         <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197740</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>91851</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492677</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005939</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>129197743</v>
       </c>
       <c r="B51" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197901</v>
+        <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>91848</v>
+        <v>83012</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492728</v>
+        <v>492677</v>
       </c>
       <c r="R52" t="n">
-        <v>7005767</v>
+        <v>7005939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B53" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,19 +6541,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6561,10 +6565,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R53" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6597,6 +6601,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6623,10 +6632,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6634,23 +6643,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R54" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6694,11 +6699,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,7 +6728,7 @@
         <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,6 +7388,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7414,10 +7419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,21 +7430,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7449,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7485,11 +7490,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7723,7 +7723,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>129170618</v>
       </c>
       <c r="B67" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R69" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98631</v>
+        <v>100916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100916</v>
+        <v>98631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1202,48 +1202,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>100916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R6" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1272,7 +1277,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1282,7 +1287,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,26 +1302,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,53 +1319,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129171977</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492601</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005770</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,6 +1414,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3288,42 +3288,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3352,7 +3347,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3362,12 +3357,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3396,12 +3386,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3419,10 +3409,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3430,37 +3420,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R23" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3489,7 +3484,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3499,7 +3494,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B24" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,6 +3622,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3648,32 +3653,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3688,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3719,11 +3724,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B31" t="n">
-        <v>91567</v>
+        <v>91573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,23 +4303,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R31" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4389,10 +4385,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B32" t="n">
-        <v>91573</v>
+        <v>91567</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4400,19 +4396,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R32" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197903</v>
+        <v>129170873</v>
       </c>
       <c r="B39" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,33 +5081,47 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492663</v>
+        <v>492543</v>
       </c>
       <c r="R39" t="n">
-        <v>7005892</v>
+        <v>7005881</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5134,11 +5148,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5147,16 +5176,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5265,10 +5319,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5276,47 +5330,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R41" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5343,26 +5383,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,51 +5396,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197749</v>
+        <v>129197774</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,23 +5423,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5447,10 +5443,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492626</v>
+        <v>492640</v>
       </c>
       <c r="R42" t="n">
-        <v>7005698</v>
+        <v>7005697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5483,11 +5479,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5611,10 +5602,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197774</v>
+        <v>129197749</v>
       </c>
       <c r="B44" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5622,19 +5613,23 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5642,10 +5637,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492640</v>
+        <v>492626</v>
       </c>
       <c r="R44" t="n">
-        <v>7005697</v>
+        <v>7005698</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5678,6 +5673,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5806,10 +5806,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197772</v>
+        <v>129197763</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,19 +5817,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5837,10 +5841,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492699</v>
+        <v>492563</v>
       </c>
       <c r="R46" t="n">
-        <v>7005773</v>
+        <v>7005801</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5873,6 +5877,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5899,7 +5908,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5934,10 +5943,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R47" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6001,48 +6010,67 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6069,14 +6097,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,83 +6125,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129172338</v>
+        <v>129197772</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492691</v>
+        <v>492699</v>
       </c>
       <c r="R49" t="n">
-        <v>7005745</v>
+        <v>7005773</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6190,26 +6210,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6218,21 +6223,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197758</v>
+        <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6541,23 +6541,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6565,10 +6561,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492465</v>
+        <v>492686</v>
       </c>
       <c r="R53" t="n">
-        <v>7005805</v>
+        <v>7005861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6601,11 +6597,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6632,10 +6623,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197776</v>
+        <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6643,19 +6634,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492686</v>
+        <v>492465</v>
       </c>
       <c r="R54" t="n">
-        <v>7005861</v>
+        <v>7005805</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6699,6 +6694,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7317,7 +7317,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197757</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492452</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005819</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7419,10 +7419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197769</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7430,21 +7430,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492718</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005812</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7490,6 +7490,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7516,10 +7521,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197769</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7527,21 +7532,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492718</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005812</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7587,11 +7592,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7618,7 +7618,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197757</v>
+        <v>129197759</v>
       </c>
       <c r="B64" t="n">
         <v>57727</v>
@@ -7653,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492452</v>
+        <v>492480</v>
       </c>
       <c r="R64" t="n">
-        <v>7005819</v>
+        <v>7005779</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197898</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492653</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005908</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gammalt bohål</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8347,7 +8347,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197764</v>
+        <v>129197898</v>
       </c>
       <c r="B71" t="n">
         <v>57727</v>
@@ -8382,10 +8382,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492665</v>
+        <v>492653</v>
       </c>
       <c r="R71" t="n">
-        <v>7005939</v>
+        <v>7005908</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>98631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98631</v>
+        <v>100916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3551,10 +3551,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R24" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,11 +3622,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3750,10 +3745,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,21 +3756,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3821,6 +3816,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3847,48 +3847,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3915,11 +3927,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3928,76 +3955,89 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>92271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4024,26 +4064,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4052,41 +4077,16 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,6 +4553,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4579,10 +4584,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4590,21 +4595,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4614,10 +4619,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4650,11 +4655,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,47 +5081,33 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R39" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5148,26 +5134,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5176,41 +5147,16 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5319,10 +5265,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129170873</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,33 +5276,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492543</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5383,11 +5343,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5396,16 +5371,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197763</v>
+        <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,23 +5817,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5841,10 +5837,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492563</v>
+        <v>492699</v>
       </c>
       <c r="R46" t="n">
-        <v>7005801</v>
+        <v>7005773</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5877,11 +5873,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5908,48 +5899,67 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R47" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,14 +5986,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5994,83 +6014,69 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129172338</v>
+        <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492691</v>
+        <v>492563</v>
       </c>
       <c r="R48" t="n">
-        <v>7005745</v>
+        <v>7005801</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6097,24 +6103,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,31 +6121,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197772</v>
+        <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6157,19 +6148,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492699</v>
+        <v>492478</v>
       </c>
       <c r="R49" t="n">
-        <v>7005773</v>
+        <v>7005840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6213,6 +6208,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,6 +6990,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7016,10 +7021,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7027,21 +7032,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7051,10 +7056,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7087,11 +7092,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7317,7 +7317,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197757</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
         <v>57727</v>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492452</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005819</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7521,10 +7521,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B63" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7532,21 +7532,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7556,10 +7556,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R63" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7592,6 +7592,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7618,10 +7623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7629,21 +7634,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7653,10 +7658,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7689,11 +7694,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8050,10 +8050,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197775</v>
+        <v>129197898</v>
       </c>
       <c r="B68" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8061,19 +8061,23 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8081,10 +8085,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492591</v>
+        <v>492653</v>
       </c>
       <c r="R68" t="n">
-        <v>7005778</v>
+        <v>7005908</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8117,6 +8121,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8143,7 +8152,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197764</v>
+        <v>129197760</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -8178,10 +8187,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492665</v>
+        <v>492512</v>
       </c>
       <c r="R69" t="n">
-        <v>7005939</v>
+        <v>7005743</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8245,7 +8254,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197760</v>
+        <v>129197764</v>
       </c>
       <c r="B70" t="n">
         <v>57727</v>
@@ -8280,10 +8289,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492512</v>
+        <v>492665</v>
       </c>
       <c r="R70" t="n">
-        <v>7005743</v>
+        <v>7005939</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8347,10 +8356,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197898</v>
+        <v>129197775</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8358,23 +8367,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8382,10 +8387,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492653</v>
+        <v>492591</v>
       </c>
       <c r="R71" t="n">
-        <v>7005908</v>
+        <v>7005778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8418,11 +8423,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1055,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171507</v>
+        <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,47 +1066,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492523</v>
+        <v>492601</v>
       </c>
       <c r="R5" t="n">
-        <v>7005882</v>
+        <v>7005770</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1145,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,12 +1164,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,38 +1187,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129173004</v>
+        <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>100916</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1242,13 +1232,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492703</v>
+        <v>492523</v>
       </c>
       <c r="R6" t="n">
-        <v>7005807</v>
+        <v>7005882</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,7 +1267,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1287,7 +1277,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,6 +1297,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,48 +1334,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129171977</v>
+        <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>100916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492601</v>
+        <v>492703</v>
       </c>
       <c r="R7" t="n">
-        <v>7005770</v>
+        <v>7005807</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1434,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129170389</v>
+        <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,23 +2749,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2774,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492643</v>
+        <v>492518</v>
       </c>
       <c r="R18" t="n">
-        <v>7005955</v>
+        <v>7005861</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2809,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2819,7 +2828,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2871,7 +2885,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B19" t="n">
         <v>91573</v>
@@ -2895,16 +2909,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2916,10 +2921,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2951,7 +2956,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,7 +2966,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3013,10 +3018,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3024,32 +3029,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R20" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3093,7 +3098,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3103,12 +3108,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3160,38 +3160,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171311</v>
+        <v>129172151</v>
       </c>
       <c r="B21" t="n">
-        <v>100916</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492624</v>
+        <v>492661</v>
       </c>
       <c r="R21" t="n">
-        <v>7005951</v>
+        <v>7005714</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,7 +3245,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3260,6 +3265,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3409,38 +3434,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129172151</v>
+        <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>100916</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3449,13 +3474,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492661</v>
+        <v>492624</v>
       </c>
       <c r="R23" t="n">
-        <v>7005714</v>
+        <v>7005951</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3484,7 +3509,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3494,12 +3519,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3514,26 +3534,6 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B31" t="n">
-        <v>91573</v>
+        <v>91567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,19 +4303,23 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4323,10 +4327,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R31" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4385,10 +4389,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B32" t="n">
-        <v>91567</v>
+        <v>91573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4396,23 +4400,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R32" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197754</v>
+        <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492459</v>
+        <v>492576</v>
       </c>
       <c r="R33" t="n">
-        <v>7005818</v>
+        <v>7005799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4553,11 +4553,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,10 +4579,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197778</v>
+        <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4595,21 +4590,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492576</v>
+        <v>492459</v>
       </c>
       <c r="R34" t="n">
-        <v>7005799</v>
+        <v>7005818</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4655,6 +4650,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5899,67 +5899,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129172338</v>
+        <v>129197763</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492691</v>
+        <v>492563</v>
       </c>
       <c r="R47" t="n">
-        <v>7005745</v>
+        <v>7005801</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5986,24 +5967,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6014,28 +5985,23 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -6070,10 +6036,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R48" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6137,48 +6103,67 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R49" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6205,14 +6190,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6223,16 +6218,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6919,10 +6919,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197755</v>
+        <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6930,21 +6930,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6954,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R57" t="n">
-        <v>7005823</v>
+        <v>7005821</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6990,11 +6990,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7021,10 +7016,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197744</v>
+        <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7032,21 +7027,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7056,10 +7051,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R58" t="n">
-        <v>7005821</v>
+        <v>7005823</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7092,6 +7087,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,11 +7388,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7419,7 +7414,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7454,10 +7449,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7521,7 +7516,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,10 +7618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7634,21 +7629,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7658,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7694,6 +7689,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B2" t="n">
-        <v>98631</v>
+        <v>100916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,36 +686,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B3" t="n">
-        <v>100916</v>
+        <v>98631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,32 +808,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171549</v>
+        <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,32 +2749,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492518</v>
+        <v>492643</v>
       </c>
       <c r="R18" t="n">
-        <v>7005861</v>
+        <v>7005955</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2818,7 +2809,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,12 +2819,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,7 +2871,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
         <v>91573</v>
@@ -2909,7 +2895,16 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2921,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2956,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2966,7 +2961,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3018,10 +3013,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129173470</v>
+        <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3029,32 +3024,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492663</v>
+        <v>492518</v>
       </c>
       <c r="R20" t="n">
-        <v>7005895</v>
+        <v>7005861</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3098,7 +3093,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3108,7 +3103,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3551,10 +3551,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R24" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,6 +3622,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3745,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3816,11 +3821,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5412,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B42" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,19 +5423,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5443,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R42" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5505,10 +5509,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,23 +5520,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R43" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B55" t="n">
-        <v>92271</v>
+        <v>91517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R55" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B56" t="n">
-        <v>91517</v>
+        <v>92271</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R56" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7720,32 +7720,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197742</v>
+        <v>129197751</v>
       </c>
       <c r="B65" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492663</v>
+        <v>492493</v>
       </c>
       <c r="R65" t="n">
-        <v>7005860</v>
+        <v>7005854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7791,6 +7791,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7817,32 +7822,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7852,10 +7857,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7888,11 +7893,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129172413</v>
+        <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>98631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492702</v>
+        <v>492564</v>
       </c>
       <c r="R2" t="n">
-        <v>7005781</v>
+        <v>7005875</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129170722</v>
+        <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>98631</v>
+        <v>100916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,36 +812,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492564</v>
+        <v>492702</v>
       </c>
       <c r="R3" t="n">
-        <v>7005875</v>
+        <v>7005781</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,34 +1816,44 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1875,7 +1885,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1885,7 +1895,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,12 +1929,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1937,10 +1952,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1948,44 +1963,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2017,7 +2022,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2027,12 +2032,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B18" t="n">
         <v>91573</v>
@@ -2762,7 +2762,16 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2774,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R18" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2809,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2819,7 +2828,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2871,7 +2880,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B19" t="n">
         <v>91573</v>
@@ -2895,16 +2904,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3160,10 +3160,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3171,42 +3171,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R21" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,12 +3240,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3279,12 +3269,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3302,10 +3292,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3313,37 +3303,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492661</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005714</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3382,7 +3377,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,11 +3622,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3653,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>91517</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3688,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3750,10 +3745,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,21 +3756,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3821,6 +3816,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B39" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5081,19 +5081,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5101,10 +5105,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R39" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5137,6 +5141,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,7 +5172,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B40" t="n">
         <v>57727</v>
@@ -5192,19 +5201,29 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R40" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5231,14 +5250,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5249,26 +5278,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5276,47 +5330,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R41" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5343,26 +5383,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5371,51 +5396,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197767</v>
+        <v>129197774</v>
       </c>
       <c r="B42" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,23 +5423,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5447,10 +5443,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492742</v>
+        <v>492640</v>
       </c>
       <c r="R42" t="n">
-        <v>7005805</v>
+        <v>7005697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5509,10 +5505,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197774</v>
+        <v>129197767</v>
       </c>
       <c r="B43" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5520,19 +5516,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5540,10 +5540,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492640</v>
+        <v>492742</v>
       </c>
       <c r="R43" t="n">
-        <v>7005697</v>
+        <v>7005805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197772</v>
+        <v>129197763</v>
       </c>
       <c r="B46" t="n">
-        <v>91573</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,19 +5817,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5837,10 +5841,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492699</v>
+        <v>492563</v>
       </c>
       <c r="R46" t="n">
-        <v>7005773</v>
+        <v>7005801</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5873,6 +5877,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5899,7 +5908,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197763</v>
+        <v>129197752</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5934,10 +5943,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492563</v>
+        <v>492478</v>
       </c>
       <c r="R47" t="n">
-        <v>7005801</v>
+        <v>7005840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6001,10 +6010,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197752</v>
+        <v>129197772</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6012,23 +6021,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6036,10 +6041,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492478</v>
+        <v>492699</v>
       </c>
       <c r="R48" t="n">
-        <v>7005840</v>
+        <v>7005773</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6072,11 +6077,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7118,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B59" t="n">
-        <v>91567</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7189,6 +7189,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7215,10 +7220,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>91567</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7226,21 +7231,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7250,10 +7255,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7286,11 +7291,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492480</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005779</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,6 +7388,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7414,7 +7419,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129197753</v>
       </c>
       <c r="B62" t="n">
         <v>57727</v>
@@ -7449,10 +7454,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492487</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005851</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7516,7 +7521,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197757</v>
       </c>
       <c r="B63" t="n">
         <v>57727</v>
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492452</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005819</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7618,10 +7623,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197757</v>
+        <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7629,21 +7634,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7653,10 +7658,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492452</v>
+        <v>492718</v>
       </c>
       <c r="R64" t="n">
-        <v>7005819</v>
+        <v>7005812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7689,11 +7694,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7720,32 +7720,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197751</v>
+        <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492493</v>
+        <v>492663</v>
       </c>
       <c r="R65" t="n">
-        <v>7005854</v>
+        <v>7005860</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7791,11 +7791,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7822,32 +7817,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197742</v>
+        <v>129197751</v>
       </c>
       <c r="B66" t="n">
-        <v>91517</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7857,10 +7852,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492663</v>
+        <v>492493</v>
       </c>
       <c r="R66" t="n">
-        <v>7005860</v>
+        <v>7005854</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7893,6 +7888,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129170722</v>
       </c>
       <c r="B2" t="n">
-        <v>98631</v>
+        <v>98660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>129172413</v>
       </c>
       <c r="B3" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>129171609</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>129171977</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>129173004</v>
       </c>
       <c r="B7" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>129171793</v>
       </c>
       <c r="B8" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129173557</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129170977</v>
+        <v>129173052</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,44 +1816,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492553</v>
+        <v>492710</v>
       </c>
       <c r="R11" t="n">
-        <v>7005901</v>
+        <v>7005821</v>
       </c>
       <c r="S11" t="n">
         <v>7</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1895,12 +1885,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,12 +1914,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1952,10 +1937,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129173052</v>
+        <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,34 +1948,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492710</v>
+        <v>492553</v>
       </c>
       <c r="R12" t="n">
-        <v>7005821</v>
+        <v>7005901</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -2022,7 +2017,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2032,7 +2027,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
         <v>129170649</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>129171830</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>129171009</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>129172075</v>
       </c>
       <c r="B16" t="n">
-        <v>98631</v>
+        <v>98660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>129173109</v>
       </c>
       <c r="B17" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B18" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2762,16 +2762,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R18" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2818,7 +2809,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,7 +2819,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2880,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129170389</v>
+        <v>129173470</v>
       </c>
       <c r="B19" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2904,7 +2895,16 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492643</v>
+        <v>492663</v>
       </c>
       <c r="R19" t="n">
-        <v>7005955</v>
+        <v>7005895</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3016,7 +3016,7 @@
         <v>129171549</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129170332</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>129172151</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>129171311</v>
       </c>
       <c r="B23" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197762</v>
       </c>
       <c r="B24" t="n">
-        <v>91517</v>
+        <v>57730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492552</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,6 +3622,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3648,32 +3653,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197904</v>
+        <v>129197895</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3683,10 +3688,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492562</v>
+        <v>492534</v>
       </c>
       <c r="R25" t="n">
-        <v>7005791</v>
+        <v>7005751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3745,10 +3750,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197904</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,21 +3761,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3780,10 +3785,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492562</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005791</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3816,11 +3821,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3850,7 +3850,7 @@
         <v>129173361</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>129197748</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>129197745</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197771</v>
+        <v>129197773</v>
       </c>
       <c r="B31" t="n">
-        <v>91567</v>
+        <v>91601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,23 +4303,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4327,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492474</v>
+        <v>492702</v>
       </c>
       <c r="R31" t="n">
-        <v>7005814</v>
+        <v>7005777</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4389,10 +4385,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197773</v>
+        <v>129197771</v>
       </c>
       <c r="B32" t="n">
-        <v>91573</v>
+        <v>91595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4400,19 +4396,23 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492702</v>
+        <v>492474</v>
       </c>
       <c r="R32" t="n">
-        <v>7005777</v>
+        <v>7005814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
         <v>129197778</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B35" t="n">
-        <v>92271</v>
+        <v>78083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B36" t="n">
-        <v>78057</v>
+        <v>92299</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4878,7 +4878,7 @@
         <v>129197777</v>
       </c>
       <c r="B37" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>129197902</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129197750</v>
+        <v>129170873</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5099,19 +5099,29 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492495</v>
+        <v>492543</v>
       </c>
       <c r="R39" t="n">
-        <v>7005861</v>
+        <v>7005881</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5138,14 +5148,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5156,26 +5176,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129170873</v>
+        <v>129197903</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5183,47 +5228,33 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492543</v>
+        <v>492663</v>
       </c>
       <c r="R40" t="n">
-        <v>7005881</v>
+        <v>7005892</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5250,26 +5281,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5278,51 +5294,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197903</v>
+        <v>129197750</v>
       </c>
       <c r="B41" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,19 +5321,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5350,10 +5345,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492663</v>
+        <v>492495</v>
       </c>
       <c r="R41" t="n">
-        <v>7005892</v>
+        <v>7005861</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5386,6 +5381,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5412,10 +5412,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197774</v>
+        <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5423,19 +5423,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5443,10 +5447,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492640</v>
+        <v>492626</v>
       </c>
       <c r="R42" t="n">
-        <v>7005697</v>
+        <v>7005698</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5479,6 +5483,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5505,10 +5514,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197767</v>
+        <v>129197756</v>
       </c>
       <c r="B43" t="n">
-        <v>91851</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5516,21 +5525,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5540,10 +5549,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492742</v>
+        <v>492452</v>
       </c>
       <c r="R43" t="n">
-        <v>7005805</v>
+        <v>7005822</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5576,6 +5585,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5602,10 +5616,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197749</v>
+        <v>129197767</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>91879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5613,21 +5627,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5637,10 +5651,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492626</v>
+        <v>492742</v>
       </c>
       <c r="R44" t="n">
-        <v>7005698</v>
+        <v>7005805</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5673,11 +5687,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5704,10 +5713,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129197756</v>
+        <v>129197774</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5715,23 +5724,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5739,10 +5744,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492452</v>
+        <v>492640</v>
       </c>
       <c r="R45" t="n">
-        <v>7005822</v>
+        <v>7005697</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5775,11 +5780,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5809,7 +5809,7 @@
         <v>129197763</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>129197752</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6010,44 +6010,67 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197772</v>
+        <v>129172338</v>
       </c>
       <c r="B48" t="n">
-        <v>91573</v>
+        <v>98756</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492699</v>
+        <v>492691</v>
       </c>
       <c r="R48" t="n">
-        <v>7005773</v>
+        <v>7005745</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6074,11 +6097,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6087,83 +6125,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129172338</v>
+        <v>129197772</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>91601</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492691</v>
+        <v>492699</v>
       </c>
       <c r="R49" t="n">
-        <v>7005745</v>
+        <v>7005773</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6190,26 +6210,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6218,31 +6223,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B51" t="n">
-        <v>91851</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>129197740</v>
       </c>
       <c r="B52" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>129197776</v>
       </c>
       <c r="B53" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197741</v>
+        <v>129197896</v>
       </c>
       <c r="B55" t="n">
-        <v>91517</v>
+        <v>92299</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492719</v>
+        <v>492539</v>
       </c>
       <c r="R55" t="n">
-        <v>7005791</v>
+        <v>7005731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197896</v>
+        <v>129197741</v>
       </c>
       <c r="B56" t="n">
-        <v>92271</v>
+        <v>91545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6833,21 +6833,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6857,10 +6857,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492539</v>
+        <v>492719</v>
       </c>
       <c r="R56" t="n">
-        <v>7005731</v>
+        <v>7005791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6922,7 +6922,7 @@
         <v>129197744</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197761</v>
+        <v>129197770</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>91595</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7129,21 +7129,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R59" t="n">
-        <v>7005736</v>
+        <v>7005794</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7189,11 +7189,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7220,10 +7215,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197770</v>
+        <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>91567</v>
+        <v>57730</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7231,21 +7226,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7255,10 +7250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492702</v>
+        <v>492512</v>
       </c>
       <c r="R60" t="n">
-        <v>7005794</v>
+        <v>7005736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7291,6 +7286,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7320,7 +7320,7 @@
         <v>129197759</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>129197753</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>129197757</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>129197769</v>
       </c>
       <c r="B64" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>129197742</v>
       </c>
       <c r="B65" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7817,48 +7817,62 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197751</v>
+        <v>129170618</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492493</v>
+        <v>492636</v>
       </c>
       <c r="R66" t="n">
-        <v>7005854</v>
+        <v>7005925</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7885,14 +7899,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7903,78 +7927,69 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129170618</v>
+        <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492636</v>
+        <v>492493</v>
       </c>
       <c r="R67" t="n">
-        <v>7005925</v>
+        <v>7005854</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8001,24 +8016,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8029,31 +8034,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197898</v>
+        <v>129197775</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>91601</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8061,23 +8061,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8085,10 +8081,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492653</v>
+        <v>492591</v>
       </c>
       <c r="R68" t="n">
-        <v>7005908</v>
+        <v>7005778</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8121,11 +8117,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8152,10 +8143,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197760</v>
+        <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8187,10 +8178,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492512</v>
+        <v>492653</v>
       </c>
       <c r="R69" t="n">
-        <v>7005743</v>
+        <v>7005908</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8227,7 +8218,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Gammalt bohål</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8254,10 +8245,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197764</v>
+        <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8289,10 +8280,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492665</v>
+        <v>492512</v>
       </c>
       <c r="R70" t="n">
-        <v>7005939</v>
+        <v>7005743</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8356,10 +8347,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197775</v>
+        <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>91573</v>
+        <v>57730</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8367,19 +8358,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8387,10 +8382,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492591</v>
+        <v>492665</v>
       </c>
       <c r="R71" t="n">
-        <v>7005778</v>
+        <v>7005939</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8423,6 +8418,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -2738,10 +2738,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129170389</v>
+        <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>91601</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2749,23 +2749,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2774,10 +2783,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492643</v>
+        <v>492518</v>
       </c>
       <c r="R18" t="n">
-        <v>7005955</v>
+        <v>7005861</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2809,7 +2818,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2819,7 +2828,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2871,7 +2885,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129173470</v>
+        <v>129170389</v>
       </c>
       <c r="B19" t="n">
         <v>91601</v>
@@ -2895,16 +2909,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -2916,10 +2921,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492663</v>
+        <v>492643</v>
       </c>
       <c r="R19" t="n">
-        <v>7005895</v>
+        <v>7005955</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2951,7 +2956,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2961,7 +2966,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3013,10 +3018,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129171549</v>
+        <v>129173470</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>91601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3024,32 +3029,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492518</v>
+        <v>492663</v>
       </c>
       <c r="R20" t="n">
-        <v>7005861</v>
+        <v>7005895</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3093,7 +3098,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3103,12 +3108,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3160,48 +3160,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129170332</v>
+        <v>129171311</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>100945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492645</v>
+        <v>492624</v>
       </c>
       <c r="R21" t="n">
-        <v>7005964</v>
+        <v>7005951</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3230,7 +3235,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3240,7 +3245,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3255,26 +3260,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3292,10 +3277,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129172151</v>
+        <v>129170332</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3303,42 +3288,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492661</v>
+        <v>492645</v>
       </c>
       <c r="R22" t="n">
-        <v>7005714</v>
+        <v>7005964</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3367,7 +3347,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3377,12 +3357,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3411,12 +3386,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3434,38 +3409,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129171311</v>
+        <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>100945</v>
+        <v>57730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3474,13 +3449,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492624</v>
+        <v>492661</v>
       </c>
       <c r="R23" t="n">
-        <v>7005951</v>
+        <v>7005714</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3509,7 +3484,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3519,7 +3494,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3534,6 +3514,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3551,32 +3551,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197762</v>
+        <v>129197895</v>
       </c>
       <c r="B24" t="n">
-        <v>57730</v>
+        <v>91545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492552</v>
+        <v>492534</v>
       </c>
       <c r="R24" t="n">
-        <v>7005798</v>
+        <v>7005751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3622,11 +3622,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3653,32 +3648,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129197895</v>
+        <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3688,10 +3683,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492534</v>
+        <v>492562</v>
       </c>
       <c r="R25" t="n">
-        <v>7005751</v>
+        <v>7005791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3750,10 +3745,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197904</v>
+        <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3761,21 +3756,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3785,10 +3780,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492562</v>
+        <v>492552</v>
       </c>
       <c r="R26" t="n">
-        <v>7005791</v>
+        <v>7005798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3821,6 +3816,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3847,60 +3847,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129173361</v>
+        <v>129197748</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>92299</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492691</v>
+        <v>492576</v>
       </c>
       <c r="R27" t="n">
-        <v>7005880</v>
+        <v>7005792</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3927,26 +3915,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3955,89 +3928,76 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129197748</v>
+        <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>92299</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R28" t="n">
-        <v>7005792</v>
+        <v>7005880</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4064,11 +4024,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4077,16 +4052,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4681,32 +4681,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197768</v>
+        <v>129197747</v>
       </c>
       <c r="B35" t="n">
-        <v>78083</v>
+        <v>92299</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492673</v>
+        <v>492738</v>
       </c>
       <c r="R35" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4778,32 +4778,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197747</v>
+        <v>129197768</v>
       </c>
       <c r="B36" t="n">
-        <v>92299</v>
+        <v>78083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492738</v>
+        <v>492673</v>
       </c>
       <c r="R36" t="n">
-        <v>7005827</v>
+        <v>7005936</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5806,10 +5806,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197763</v>
+        <v>129197772</v>
       </c>
       <c r="B46" t="n">
-        <v>57730</v>
+        <v>91601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,23 +5817,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5841,10 +5837,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492563</v>
+        <v>492699</v>
       </c>
       <c r="R46" t="n">
-        <v>7005801</v>
+        <v>7005773</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5877,11 +5873,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5908,48 +5899,67 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197752</v>
+        <v>129172338</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492478</v>
+        <v>492691</v>
       </c>
       <c r="R47" t="n">
-        <v>7005840</v>
+        <v>7005745</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5976,14 +5986,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5994,83 +6014,69 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129172338</v>
+        <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492691</v>
+        <v>492563</v>
       </c>
       <c r="R48" t="n">
-        <v>7005745</v>
+        <v>7005801</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6097,24 +6103,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6125,31 +6121,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197772</v>
+        <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>91601</v>
+        <v>57730</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6157,19 +6148,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6177,10 +6172,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492699</v>
+        <v>492478</v>
       </c>
       <c r="R49" t="n">
-        <v>7005773</v>
+        <v>7005840</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6213,6 +6208,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197901</v>
+        <v>129197743</v>
       </c>
       <c r="B50" t="n">
-        <v>91879</v>
+        <v>91581</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492728</v>
+        <v>492617</v>
       </c>
       <c r="R50" t="n">
-        <v>7005767</v>
+        <v>7005729</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197743</v>
+        <v>129197901</v>
       </c>
       <c r="B51" t="n">
-        <v>91581</v>
+        <v>91879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492617</v>
+        <v>492728</v>
       </c>
       <c r="R51" t="n">
-        <v>7005729</v>
+        <v>7005767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7317,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197759</v>
+        <v>129197769</v>
       </c>
       <c r="B61" t="n">
-        <v>57730</v>
+        <v>91577</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7328,21 +7328,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492480</v>
+        <v>492718</v>
       </c>
       <c r="R61" t="n">
-        <v>7005779</v>
+        <v>7005812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7388,11 +7388,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7419,7 +7414,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197753</v>
+        <v>129197759</v>
       </c>
       <c r="B62" t="n">
         <v>57730</v>
@@ -7454,10 +7449,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492487</v>
+        <v>492480</v>
       </c>
       <c r="R62" t="n">
-        <v>7005851</v>
+        <v>7005779</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7521,7 +7516,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197757</v>
+        <v>129197753</v>
       </c>
       <c r="B63" t="n">
         <v>57730</v>
@@ -7556,10 +7551,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492452</v>
+        <v>492487</v>
       </c>
       <c r="R63" t="n">
-        <v>7005819</v>
+        <v>7005851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7623,10 +7618,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197769</v>
+        <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>91577</v>
+        <v>57730</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7634,21 +7629,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7658,10 +7653,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492718</v>
+        <v>492452</v>
       </c>
       <c r="R64" t="n">
-        <v>7005812</v>
+        <v>7005819</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7694,6 +7689,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3947,7 +3947,7 @@
         <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4183,12 +4183,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
         <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4669,12 +4669,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
         <v>129170873</v>
       </c>
       <c r="B39" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>129197750</v>
       </c>
       <c r="B41" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5400,12 +5400,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5415,7 +5415,7 @@
         <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5502,12 +5502,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5517,7 +5517,7 @@
         <v>129197756</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5604,12 +5604,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
         <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6125,12 +6125,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6140,7 +6140,7 @@
         <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6227,12 +6227,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6626,7 +6626,7 @@
         <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6713,12 +6713,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7019,7 +7019,7 @@
         <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7106,12 +7106,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
         <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7305,12 +7305,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7417,7 +7417,7 @@
         <v>129197759</v>
       </c>
       <c r="B62" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7504,12 +7504,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7519,7 +7519,7 @@
         <v>129197753</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7606,12 +7606,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7621,7 +7621,7 @@
         <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7708,12 +7708,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7951,7 +7951,7 @@
         <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8038,12 +8038,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8146,7 +8146,7 @@
         <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,12 +8233,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8248,7 +8248,7 @@
         <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8335,12 +8335,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
         <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8437,12 +8437,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>129170873</v>
       </c>
       <c r="B39" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>129197750</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>129197756</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>129197759</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>129197753</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -1190,7 +1190,7 @@
         <v>129171507</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>129171353</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>129170977</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>129171549</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>129172151</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>129197762</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>129173361</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>129197899</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>129197754</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>129170873</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>129197750</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>129197749</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>129197756</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>129197752</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>129197758</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>129197755</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>129197761</v>
       </c>
       <c r="B60" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>129197759</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>129197753</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>129197757</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>129197751</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>129197898</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>129197760</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>129197764</v>
       </c>
       <c r="B71" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129170722</v>
+        <v>129197767</v>
       </c>
       <c r="B2" t="n">
-        <v>98660</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492564</v>
+        <v>492742</v>
       </c>
       <c r="R2" t="n">
-        <v>7005875</v>
+        <v>7005805</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,21 +743,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -780,79 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129172413</v>
+        <v>129197901</v>
       </c>
       <c r="B3" t="n">
-        <v>100945</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492702</v>
+        <v>492728</v>
       </c>
       <c r="R3" t="n">
-        <v>7005781</v>
+        <v>7005767</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,21 +840,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,31 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129171609</v>
+        <v>129197769</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492541</v>
+        <v>492718</v>
       </c>
       <c r="R4" t="n">
-        <v>7005833</v>
+        <v>7005812</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,21 +937,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1014,51 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129171977</v>
+        <v>129197743</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492601</v>
+        <v>492617</v>
       </c>
       <c r="R5" t="n">
-        <v>7005770</v>
+        <v>7005729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,21 +1034,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1146,51 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129171507</v>
+        <v>129197744</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,47 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492523</v>
+        <v>492718</v>
       </c>
       <c r="R6" t="n">
-        <v>7005882</v>
+        <v>7005821</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,26 +1131,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1293,94 +1144,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129173004</v>
+        <v>129197745</v>
       </c>
       <c r="B7" t="n">
-        <v>100945</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492703</v>
+        <v>492681</v>
       </c>
       <c r="R7" t="n">
-        <v>7005807</v>
+        <v>7005731</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,21 +1228,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,69 +1241,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129171793</v>
+        <v>129197770</v>
       </c>
       <c r="B8" t="n">
-        <v>97633</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492585</v>
+        <v>492702</v>
       </c>
       <c r="R8" t="n">
-        <v>7005755</v>
+        <v>7005794</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1519,21 +1325,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1542,69 +1338,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129173557</v>
+        <v>129197771</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492602</v>
+        <v>492474</v>
       </c>
       <c r="R9" t="n">
-        <v>7005837</v>
+        <v>7005814</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1648,68 +1439,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129171353</v>
+        <v>129197747</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492590</v>
+        <v>492738</v>
       </c>
       <c r="R10" t="n">
-        <v>7005936</v>
+        <v>7005827</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,26 +1519,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1764,89 +1532,64 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129173052</v>
+        <v>129197748</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492710</v>
+        <v>492576</v>
       </c>
       <c r="R11" t="n">
-        <v>7005821</v>
+        <v>7005792</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,21 +1616,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1896,99 +1629,64 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129170977</v>
+        <v>129197896</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492553</v>
+        <v>492539</v>
       </c>
       <c r="R12" t="n">
-        <v>7005901</v>
+        <v>7005731</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,26 +1713,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2043,86 +1726,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129170649</v>
+        <v>129197741</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492595</v>
+        <v>492719</v>
       </c>
       <c r="R13" t="n">
-        <v>7005894</v>
+        <v>7005791</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2152,21 +1810,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2175,86 +1823,61 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129171830</v>
+        <v>129197742</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492595</v>
+        <v>492663</v>
       </c>
       <c r="R14" t="n">
-        <v>7005756</v>
+        <v>7005860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2284,21 +1907,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2307,89 +1920,64 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129171009</v>
+        <v>129197895</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492558</v>
+        <v>492534</v>
       </c>
       <c r="R15" t="n">
-        <v>7005894</v>
+        <v>7005751</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2416,26 +2004,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2444,105 +2017,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129172075</v>
+        <v>129170332</v>
       </c>
       <c r="B16" t="n">
-        <v>98660</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492616</v>
+        <v>492645</v>
       </c>
       <c r="R16" t="n">
-        <v>7005716</v>
+        <v>7005964</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2574,7 +2103,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2584,12 +2113,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 fröställning i gammal granskog.</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2604,6 +2128,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2621,53 +2165,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129173109</v>
+        <v>129170649</v>
       </c>
       <c r="B17" t="n">
-        <v>100945</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492723</v>
+        <v>492595</v>
       </c>
       <c r="R17" t="n">
-        <v>7005869</v>
+        <v>7005894</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2696,7 +2235,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2706,7 +2245,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2721,6 +2260,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2738,55 +2297,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129171549</v>
+        <v>129171009</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492518</v>
+        <v>492558</v>
       </c>
       <c r="R18" t="n">
-        <v>7005861</v>
+        <v>7005894</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2818,7 +2367,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2828,12 +2377,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2862,12 +2411,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2885,49 +2434,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129170389</v>
+        <v>129171609</v>
       </c>
       <c r="B19" t="n">
-        <v>91601</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492643</v>
+        <v>492541</v>
       </c>
       <c r="R19" t="n">
-        <v>7005955</v>
+        <v>7005833</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2956,7 +2504,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2966,7 +2514,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2995,12 +2543,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3018,58 +2566,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129173470</v>
+        <v>129171830</v>
       </c>
       <c r="B20" t="n">
-        <v>91601</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492663</v>
+        <v>492595</v>
       </c>
       <c r="R20" t="n">
-        <v>7005895</v>
+        <v>7005756</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3098,7 +2636,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3108,7 +2646,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3137,12 +2675,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3160,50 +2698,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129171311</v>
+        <v>129171977</v>
       </c>
       <c r="B21" t="n">
-        <v>100945</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492624</v>
+        <v>492601</v>
       </c>
       <c r="R21" t="n">
-        <v>7005951</v>
+        <v>7005770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3235,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3245,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3260,6 +2793,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3277,14 +2830,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129170332</v>
+        <v>129173052</v>
       </c>
       <c r="B22" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3312,13 +2865,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492645</v>
+        <v>492710</v>
       </c>
       <c r="R22" t="n">
-        <v>7005964</v>
+        <v>7005821</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3347,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3357,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,53 +2962,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129172151</v>
+        <v>129173557</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492661</v>
+        <v>492602</v>
       </c>
       <c r="R23" t="n">
-        <v>7005714</v>
+        <v>7005837</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3482,26 +3030,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3510,31 +3043,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3551,32 +3059,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129197895</v>
+        <v>129197778</v>
       </c>
       <c r="B24" t="n">
-        <v>91545</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3586,10 +3094,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492534</v>
+        <v>492576</v>
       </c>
       <c r="R24" t="n">
-        <v>7005751</v>
+        <v>7005799</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3636,12 +3144,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3651,11 +3159,11 @@
         <v>129197904</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3733,22 +3241,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129197762</v>
+        <v>129197740</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,21 +3264,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3780,10 +3288,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492552</v>
+        <v>492677</v>
       </c>
       <c r="R26" t="n">
-        <v>7005798</v>
+        <v>7005939</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3816,11 +3324,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3847,48 +3350,58 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129197748</v>
+        <v>129170873</v>
       </c>
       <c r="B27" t="n">
-        <v>92299</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492576</v>
+        <v>492543</v>
       </c>
       <c r="R27" t="n">
-        <v>7005792</v>
+        <v>7005881</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3915,11 +3428,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3928,26 +3456,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129173361</v>
+        <v>129170977</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3973,8 +3526,6 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -3991,13 +3542,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492691</v>
+        <v>492553</v>
       </c>
       <c r="R28" t="n">
-        <v>7005880</v>
+        <v>7005901</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4026,7 +3577,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4036,12 +3587,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+          <t>Ringhack (savhack), färska, på en smal gran vid en gammal hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4093,10 +3644,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129197899</v>
+        <v>129171353</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4122,19 +3673,27 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492662</v>
+        <v>492590</v>
       </c>
       <c r="R29" t="n">
-        <v>7005963</v>
+        <v>7005936</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4161,14 +3720,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4179,26 +3748,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129197745</v>
+        <v>129171507</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4206,37 +3800,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492681</v>
+        <v>492523</v>
       </c>
       <c r="R30" t="n">
-        <v>7005731</v>
+        <v>7005882</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4263,11 +3867,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4276,26 +3895,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129197773</v>
+        <v>129171549</v>
       </c>
       <c r="B31" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4303,33 +3947,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492702</v>
+        <v>492518</v>
       </c>
       <c r="R31" t="n">
-        <v>7005777</v>
+        <v>7005861</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4356,11 +4014,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid en gammal hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4369,26 +4042,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129197771</v>
+        <v>129172151</v>
       </c>
       <c r="B32" t="n">
-        <v>91595</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4396,37 +4094,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492474</v>
+        <v>492661</v>
       </c>
       <c r="R32" t="n">
-        <v>7005814</v>
+        <v>7005714</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4453,11 +4156,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4466,26 +4184,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197778</v>
+        <v>129173361</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4493,37 +4236,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492576</v>
+        <v>492691</v>
       </c>
       <c r="R33" t="n">
-        <v>7005799</v>
+        <v>7005880</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4550,11 +4305,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran i gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4563,26 +4333,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197754</v>
+        <v>129197749</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4614,10 +4409,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492459</v>
+        <v>492626</v>
       </c>
       <c r="R34" t="n">
-        <v>7005818</v>
+        <v>7005698</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4681,32 +4476,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197747</v>
+        <v>129197750</v>
       </c>
       <c r="B35" t="n">
-        <v>92299</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4716,10 +4511,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492738</v>
+        <v>492495</v>
       </c>
       <c r="R35" t="n">
-        <v>7005827</v>
+        <v>7005861</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4754,6 +4549,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4766,22 +4566,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129197768</v>
+        <v>129197751</v>
       </c>
       <c r="B36" t="n">
-        <v>78083</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,21 +4589,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4813,10 +4613,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492673</v>
+        <v>492493</v>
       </c>
       <c r="R36" t="n">
-        <v>7005936</v>
+        <v>7005854</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4851,6 +4651,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4863,22 +4668,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129197777</v>
+        <v>129197752</v>
       </c>
       <c r="B37" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4886,19 +4691,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4906,10 +4715,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492658</v>
+        <v>492478</v>
       </c>
       <c r="R37" t="n">
-        <v>7005841</v>
+        <v>7005840</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4944,6 +4753,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4956,44 +4770,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129197902</v>
+        <v>129197753</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5003,10 +4817,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492671</v>
+        <v>492487</v>
       </c>
       <c r="R38" t="n">
-        <v>7005882</v>
+        <v>7005851</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5043,7 +4857,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt, över 100st bladrosetter</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5058,22 +4872,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129170873</v>
+        <v>129197754</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5099,29 +4913,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492543</v>
+        <v>492459</v>
       </c>
       <c r="R39" t="n">
-        <v>7005881</v>
+        <v>7005818</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5148,24 +4952,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en gammal hyggeskant.</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,51 +4970,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129197903</v>
+        <v>129197755</v>
       </c>
       <c r="B40" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5228,19 +4997,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5248,10 +5021,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492663</v>
+        <v>492452</v>
       </c>
       <c r="R40" t="n">
-        <v>7005892</v>
+        <v>7005823</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5286,6 +5059,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5298,22 +5076,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129197750</v>
+        <v>129197756</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5345,10 +5123,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492495</v>
+        <v>492452</v>
       </c>
       <c r="R41" t="n">
-        <v>7005861</v>
+        <v>7005822</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5385,7 +5163,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5412,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129197749</v>
+        <v>129197757</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5447,10 +5225,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492626</v>
+        <v>492452</v>
       </c>
       <c r="R42" t="n">
-        <v>7005698</v>
+        <v>7005819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5487,7 +5265,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5514,10 +5292,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129197756</v>
+        <v>129197758</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5549,10 +5327,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492452</v>
+        <v>492465</v>
       </c>
       <c r="R43" t="n">
-        <v>7005822</v>
+        <v>7005805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5589,7 +5367,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5616,10 +5394,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129197767</v>
+        <v>129197759</v>
       </c>
       <c r="B44" t="n">
-        <v>91879</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5627,21 +5405,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5651,10 +5429,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492742</v>
+        <v>492480</v>
       </c>
       <c r="R44" t="n">
-        <v>7005805</v>
+        <v>7005779</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5689,6 +5467,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5701,22 +5484,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129197774</v>
+        <v>129197760</v>
       </c>
       <c r="B45" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5724,19 +5507,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5744,10 +5531,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492640</v>
+        <v>492512</v>
       </c>
       <c r="R45" t="n">
-        <v>7005697</v>
+        <v>7005743</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5782,6 +5569,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5794,22 +5586,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129197772</v>
+        <v>129197761</v>
       </c>
       <c r="B46" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5817,19 +5609,23 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5837,10 +5633,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492699</v>
+        <v>492512</v>
       </c>
       <c r="R46" t="n">
-        <v>7005773</v>
+        <v>7005736</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5875,6 +5671,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5887,79 +5688,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129172338</v>
+        <v>129197762</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492691</v>
+        <v>492552</v>
       </c>
       <c r="R47" t="n">
-        <v>7005745</v>
+        <v>7005798</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5986,24 +5768,14 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6014,21 +5786,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6038,7 +5805,7 @@
         <v>129197763</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6137,10 +5904,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197752</v>
+        <v>129197764</v>
       </c>
       <c r="B49" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6172,10 +5939,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492478</v>
+        <v>492665</v>
       </c>
       <c r="R49" t="n">
-        <v>7005840</v>
+        <v>7005939</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,10 +6006,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197743</v>
+        <v>129197897</v>
       </c>
       <c r="B50" t="n">
-        <v>91581</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6250,21 +6017,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6274,10 +6041,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492617</v>
+        <v>492464</v>
       </c>
       <c r="R50" t="n">
-        <v>7005729</v>
+        <v>7005838</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6312,6 +6079,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6324,22 +6096,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129197901</v>
+        <v>129197898</v>
       </c>
       <c r="B51" t="n">
-        <v>91879</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6347,21 +6119,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6371,10 +6143,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492728</v>
+        <v>492653</v>
       </c>
       <c r="R51" t="n">
-        <v>7005767</v>
+        <v>7005908</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6409,6 +6181,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gammalt bohål</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6421,22 +6198,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197740</v>
+        <v>129197899</v>
       </c>
       <c r="B52" t="n">
-        <v>83039</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6444,21 +6221,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6468,10 +6245,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492677</v>
+        <v>492662</v>
       </c>
       <c r="R52" t="n">
-        <v>7005939</v>
+        <v>7005963</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,6 +6283,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6518,56 +6300,74 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197776</v>
+        <v>129170722</v>
       </c>
       <c r="B53" t="n">
-        <v>91601</v>
+        <v>99022</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492686</v>
+        <v>492564</v>
       </c>
       <c r="R53" t="n">
-        <v>7005861</v>
+        <v>7005875</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6594,11 +6394,21 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6607,64 +6417,88 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197758</v>
+        <v>129172075</v>
       </c>
       <c r="B54" t="n">
-        <v>57740</v>
+        <v>99022</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492465</v>
+        <v>492616</v>
       </c>
       <c r="R54" t="n">
-        <v>7005805</v>
+        <v>7005716</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6691,14 +6525,24 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>1 fröställning i gammal granskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6709,64 +6553,83 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197896</v>
+        <v>129170618</v>
       </c>
       <c r="B55" t="n">
-        <v>92299</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492539</v>
+        <v>492636</v>
       </c>
       <c r="R55" t="n">
-        <v>7005731</v>
+        <v>7005925</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6793,11 +6656,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6806,64 +6684,88 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129197741</v>
+        <v>129172338</v>
       </c>
       <c r="B56" t="n">
-        <v>91545</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492719</v>
+        <v>492691</v>
       </c>
       <c r="R56" t="n">
-        <v>7005791</v>
+        <v>7005745</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6890,11 +6792,26 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 44 plantor inom ca 2 x 1 m2 yta i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6903,48 +6820,53 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129197744</v>
+        <v>129197902</v>
       </c>
       <c r="B57" t="n">
-        <v>91581</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6954,10 +6876,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492718</v>
+        <v>492671</v>
       </c>
       <c r="R57" t="n">
-        <v>7005821</v>
+        <v>7005882</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6992,6 +6914,11 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt, över 100st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7004,60 +6931,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129197755</v>
+        <v>129171793</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492452</v>
+        <v>492585</v>
       </c>
       <c r="R58" t="n">
-        <v>7005823</v>
+        <v>7005755</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7084,14 +7011,19 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7102,61 +7034,71 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197770</v>
+        <v>129171311</v>
       </c>
       <c r="B59" t="n">
-        <v>91595</v>
+        <v>101325</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492702</v>
+        <v>492624</v>
       </c>
       <c r="R59" t="n">
-        <v>7005794</v>
+        <v>7005951</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7186,11 +7128,21 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7199,64 +7151,79 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197761</v>
+        <v>129172413</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>101325</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492512</v>
+        <v>492702</v>
       </c>
       <c r="R60" t="n">
-        <v>7005736</v>
+        <v>7005781</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7283,14 +7250,19 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7301,64 +7273,74 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197769</v>
+        <v>129173004</v>
       </c>
       <c r="B61" t="n">
-        <v>91577</v>
+        <v>101325</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492718</v>
+        <v>492703</v>
       </c>
       <c r="R61" t="n">
-        <v>7005812</v>
+        <v>7005807</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7385,11 +7367,21 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7398,64 +7390,74 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197759</v>
+        <v>129173109</v>
       </c>
       <c r="B62" t="n">
-        <v>57740</v>
+        <v>101325</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Älggropbrännan, Jmt</t>
+          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492480</v>
+        <v>492723</v>
       </c>
       <c r="R62" t="n">
-        <v>7005779</v>
+        <v>7005869</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7482,14 +7484,19 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7500,26 +7507,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129197753</v>
+        <v>129197768</v>
       </c>
       <c r="B63" t="n">
-        <v>57740</v>
+        <v>78339</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7527,21 +7539,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7551,10 +7563,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492487</v>
+        <v>492673</v>
       </c>
       <c r="R63" t="n">
-        <v>7005851</v>
+        <v>7005936</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7589,11 +7601,6 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7615,837 +7622,6 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>129197757</v>
-      </c>
-      <c r="B64" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>492452</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7005819</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>129197742</v>
-      </c>
-      <c r="B65" t="n">
-        <v>91545</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>492663</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7005860</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Marielle Andersson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Marielle Andersson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>129170618</v>
-      </c>
-      <c r="B66" t="n">
-        <v>98756</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>492636</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7005925</v>
-      </c>
-      <c r="S66" t="n">
-        <v>9</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 2 m2 yta.</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>129197751</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>492493</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7005854</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>129197775</v>
-      </c>
-      <c r="B68" t="n">
-        <v>91601</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>492591</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7005778</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Marielle Andersson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Marielle Andersson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>129197898</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>492653</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7005908</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Gammalt bohål</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>129197760</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>492512</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7005743</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>129197764</v>
-      </c>
-      <c r="B71" t="n">
-        <v>57740</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Älggropbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>492665</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7005939</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Brunflo</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47954-2025 artfynd.xlsx
+++ b/artfynd/A 47954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197769</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197744</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197745</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197771</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197747</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197748</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197896</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197741</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197742</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197895</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170332</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170649</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171009</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171609</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2695,6 +2790,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171830</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171977</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,6 +3064,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173052</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3056,6 +3166,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173557</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197778</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3250,6 +3370,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197904</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197740</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3494,6 +3624,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170873</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3641,6 +3776,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170977</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3786,6 +3926,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171353</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3933,6 +4078,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171507</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4080,6 +4230,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171549</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4222,6 +4377,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129172151</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4371,6 +4531,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173361</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4473,6 +4638,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197749</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4575,6 +4745,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197750</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4677,6 +4852,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197751</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4779,6 +4959,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197752</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4881,6 +5066,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197753</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4983,6 +5173,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197754</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5085,6 +5280,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197755</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5187,6 +5387,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197756</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5289,6 +5494,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197757</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5391,6 +5601,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197758</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5493,6 +5708,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197759</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5595,6 +5815,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197760</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5697,6 +5922,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197761</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5799,6 +6029,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197762</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5901,6 +6136,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197763</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6003,6 +6243,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197764</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6105,6 +6350,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197897</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6207,6 +6457,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197898</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6309,6 +6564,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197899</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6435,6 +6695,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170722</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6571,6 +6836,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129172075</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6702,6 +6972,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170618</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6838,6 +7113,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129172338</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6940,6 +7220,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197902</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7052,6 +7337,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171793</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7169,6 +7459,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129171311</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7291,6 +7586,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129172413</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7408,6 +7708,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173004</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7525,6 +7830,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129173109</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7622,8 +7932,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>